--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220820C-0801-48CB-8BB0-795848D06F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD363E32-34CE-41BF-A6D9-514B0BD81125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="278">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,6 +869,9 @@
   </si>
   <si>
     <t>PDef1</t>
+  </si>
+  <si>
+    <t>LVA</t>
   </si>
 </sst>
 </file>
@@ -3218,15 +3221,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3269,6 +3272,9 @@
       </c>
     </row>
     <row r="5" spans="2:8">
+      <c r="C5" t="s">
+        <v>277</v>
+      </c>
       <c r="F5" t="s">
         <v>37</v>
       </c>
@@ -3285,19 +3291,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="18" thickBot="1">
+    <row r="3" spans="2:18" ht="17.5" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3316,7 +3322,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -4193,15 +4199,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="6"/>
-    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="9.1796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="6"/>
+    <col min="4" max="4" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.453125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4232,7 +4238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15">
+    <row r="12" spans="2:7" ht="14.5">
       <c r="B12" s="7" t="s">
         <v>276</v>
       </c>
@@ -4252,7 +4258,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15">
+    <row r="13" spans="2:7" ht="14.5">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -4260,7 +4266,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15">
+    <row r="14" spans="2:7" ht="14.5">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -4280,7 +4286,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15">
+    <row r="15" spans="2:7" ht="14.5">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -4300,7 +4306,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15">
+    <row r="16" spans="2:7" ht="14.5">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -4320,7 +4326,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15">
+    <row r="17" spans="2:7" ht="14.5">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -4340,7 +4346,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15">
+    <row r="18" spans="2:7" ht="14.5">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -4360,7 +4366,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15">
+    <row r="19" spans="2:7" ht="14.5">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -4376,7 +4382,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15">
+    <row r="20" spans="2:7" ht="14.5">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -4388,7 +4394,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15">
+    <row r="21" spans="2:7" ht="14.5">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -4396,7 +4402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15">
+    <row r="22" spans="2:7" ht="14.5">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -4404,7 +4410,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15">
+    <row r="23" spans="2:7" ht="14.5">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -4412,7 +4418,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15">
+    <row r="24" spans="2:7" ht="14.5">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -4420,46 +4426,46 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15">
+    <row r="25" spans="2:7" ht="14.5">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15">
+    <row r="26" spans="2:7" ht="14.5">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15">
+    <row r="27" spans="2:7" ht="14.5">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15">
+    <row r="28" spans="2:7" ht="14.5">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="15">
+    <row r="29" spans="2:7" ht="14.5">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="15">
+    <row r="30" spans="2:7" ht="14.5">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="15">
+    <row r="31" spans="2:7" ht="14.5">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="15">
+    <row r="32" spans="2:7" ht="14.5">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" spans="2:2" ht="14.5">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -4471,28 +4477,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="11"/>
+    <col min="2" max="2" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="11"/>
+    <col min="9" max="9" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.453125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
+    <row r="1" spans="2:12" ht="12.5">
       <c r="B1" s="6"/>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:12" ht="12.75">
+    <row r="2" spans="2:12" ht="12.5">
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -4503,7 +4509,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="2:12" ht="12.75">
+    <row r="3" spans="2:12" ht="12.5">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4522,7 +4528,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" ht="12">
       <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
@@ -4631,7 +4637,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" ht="12">
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
@@ -4679,7 +4685,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.75">
+    <row r="18" spans="2:14" ht="12.5">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4690,7 +4696,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="12.75">
+    <row r="19" spans="2:14" ht="12.5">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -4701,7 +4707,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="12.75">
+    <row r="20" spans="2:14" ht="12.5">
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -4712,7 +4718,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
+    <row r="21" spans="2:14" ht="14.5">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4727,7 +4733,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="15">
+    <row r="22" spans="2:14" ht="14.5">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4742,7 +4748,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="15">
+    <row r="23" spans="2:14" ht="14.5">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4757,7 +4763,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="15">
+    <row r="24" spans="2:14" ht="14.5">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4772,7 +4778,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="15">
+    <row r="25" spans="2:14" ht="14.5">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4787,7 +4793,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="15">
+    <row r="26" spans="2:14" ht="14.5">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4802,7 +4808,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="15">
+    <row r="27" spans="2:14" ht="14.5">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4817,7 +4823,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="15">
+    <row r="28" spans="2:14" ht="14.5">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4832,7 +4838,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="15">
+    <row r="29" spans="2:14" ht="14.5">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4847,7 +4853,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="15">
+    <row r="30" spans="2:14" ht="14.5">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4862,7 +4868,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="15">
+    <row r="31" spans="2:14" ht="14.5">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4877,7 +4883,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="15">
+    <row r="32" spans="2:14" ht="14.5">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4892,7 +4898,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="15">
+    <row r="33" spans="2:14" ht="14.5">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4907,7 +4913,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="15">
+    <row r="34" spans="2:14" ht="14.5">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4922,7 +4928,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="15">
+    <row r="35" spans="2:14" ht="14.5">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4937,7 +4943,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="15">
+    <row r="36" spans="2:14" ht="14.5">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4952,7 +4958,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="15">
+    <row r="37" spans="2:14" ht="14.5">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4967,7 +4973,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="15">
+    <row r="38" spans="2:14" ht="14.5">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4982,7 +4988,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="15">
+    <row r="39" spans="2:14" ht="14.5">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -4997,7 +5003,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="15">
+    <row r="40" spans="2:14" ht="14.5">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5012,7 +5018,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="15">
+    <row r="41" spans="2:14" ht="14.5">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5027,7 +5033,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="15">
+    <row r="42" spans="2:14" ht="14.5">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5052,25 +5058,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="11"/>
-    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="11"/>
+    <col min="2" max="2" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" style="11"/>
+    <col min="5" max="5" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="11"/>
-    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="11"/>
+    <col min="10" max="10" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" style="11"/>
+    <col min="12" max="12" width="17.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.453125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="18" thickBot="1">
+    <row r="2" spans="1:14" ht="17.5" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -5084,7 +5090,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -5117,7 +5123,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -5142,7 +5148,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -5169,7 +5175,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -5190,7 +5196,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -5211,7 +5217,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -5238,7 +5244,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -5265,7 +5271,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -5292,7 +5298,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -5319,7 +5325,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -5346,7 +5352,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -5373,7 +5379,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -5400,7 +5406,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -5427,7 +5433,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -5454,7 +5460,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -5481,7 +5487,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -5507,7 +5513,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -5533,7 +5539,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -5559,7 +5565,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -5585,7 +5591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -5611,7 +5617,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5637,7 +5643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -5663,7 +5669,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -5689,7 +5695,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -5706,7 +5712,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -5723,7 +5729,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -5740,7 +5746,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.5">
+    <row r="29" spans="1:14" ht="13">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -5757,7 +5763,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.5">
+    <row r="30" spans="1:14" ht="13">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -5774,7 +5780,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.5">
+    <row r="31" spans="1:14" ht="13">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -5791,7 +5797,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.5">
+    <row r="32" spans="1:14" ht="13">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -5808,7 +5814,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.5">
+    <row r="33" spans="2:9" ht="13">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -5825,7 +5831,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5">
+    <row r="34" spans="2:9" ht="13">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -5842,7 +5848,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5">
+    <row r="35" spans="2:9" ht="13">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -5859,7 +5865,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.5">
+    <row r="36" spans="2:9" ht="13">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -5876,7 +5882,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.5">
+    <row r="37" spans="2:9" ht="13">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -5893,7 +5899,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.5">
+    <row r="38" spans="2:9" ht="13">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5">
+    <row r="39" spans="2:9" ht="13">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -5927,7 +5933,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.5">
+    <row r="40" spans="2:9" ht="13">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -5944,7 +5950,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.5">
+    <row r="41" spans="2:9" ht="13">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -5961,7 +5967,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.5">
+    <row r="42" spans="2:9" ht="13">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.5">
+    <row r="43" spans="2:9" ht="13">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -5995,7 +6001,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.5">
+    <row r="44" spans="2:9" ht="13">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -6012,7 +6018,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.5">
+    <row r="45" spans="2:9" ht="13">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -6029,7 +6035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.5">
+    <row r="46" spans="2:9" ht="13">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -6046,7 +6052,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.5">
+    <row r="47" spans="2:9" ht="13">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -6063,7 +6069,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.5">
+    <row r="48" spans="2:9" ht="13">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -6080,7 +6086,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.5">
+    <row r="49" spans="2:9" ht="13">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -6097,7 +6103,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.5">
+    <row r="50" spans="2:9" ht="13">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -6114,7 +6120,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.5">
+    <row r="51" spans="2:9" ht="13">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -6134,7 +6140,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.5">
+    <row r="52" spans="2:9" ht="13">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -6148,7 +6154,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.5">
+    <row r="53" spans="2:9" ht="13">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -6162,7 +6168,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.5">
+    <row r="54" spans="2:9" ht="13">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -6628,12 +6634,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="18" thickBot="1">
+    <row r="99" spans="5:10" ht="17.5" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>48</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="15">
+    <row r="101" spans="5:10" ht="14.5">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -6669,7 +6675,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="15">
+    <row r="102" spans="5:10" ht="14.5">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -6692,19 +6698,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="6"/>
-    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="2" width="8.81640625" style="6"/>
+    <col min="3" max="3" width="20.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18" thickBot="1">
+    <row r="3" spans="2:4" ht="17.5" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
@@ -6891,17 +6897,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" ht="13">
       <c r="B23" s="18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="18" thickBot="1">
+    <row r="25" spans="2:4" ht="17.5" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD363E32-34CE-41BF-A6D9-514B0BD81125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40783C0B-64A0-4CE9-82D0-250664437A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="277">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,9 +869,6 @@
   </si>
   <si>
     <t>PDef1</t>
-  </si>
-  <si>
-    <t>LVA</t>
   </si>
 </sst>
 </file>
@@ -1227,6 +1224,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3221,15 +3220,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3272,9 +3271,6 @@
       </c>
     </row>
     <row r="5" spans="2:8">
-      <c r="C5" t="s">
-        <v>277</v>
-      </c>
       <c r="F5" t="s">
         <v>37</v>
       </c>
@@ -3291,19 +3287,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.5" thickBot="1">
+    <row r="3" spans="2:18" ht="18" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3322,7 +3318,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -4199,15 +4195,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="6"/>
-    <col min="4" max="4" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="6"/>
+    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="6"/>
+    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4238,7 +4234,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.5">
+    <row r="12" spans="2:7" ht="15">
       <c r="B12" s="7" t="s">
         <v>276</v>
       </c>
@@ -4258,7 +4254,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.5">
+    <row r="13" spans="2:7" ht="15">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -4266,7 +4262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.5">
+    <row r="14" spans="2:7" ht="15">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -4286,7 +4282,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.5">
+    <row r="15" spans="2:7" ht="15">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -4306,7 +4302,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.5">
+    <row r="16" spans="2:7" ht="15">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -4326,7 +4322,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.5">
+    <row r="17" spans="2:7" ht="15">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -4346,7 +4342,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.5">
+    <row r="18" spans="2:7" ht="15">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -4366,7 +4362,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.5">
+    <row r="19" spans="2:7" ht="15">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -4382,7 +4378,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.5">
+    <row r="20" spans="2:7" ht="15">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -4394,7 +4390,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.5">
+    <row r="21" spans="2:7" ht="15">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -4402,7 +4398,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.5">
+    <row r="22" spans="2:7" ht="15">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -4410,7 +4406,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.5">
+    <row r="23" spans="2:7" ht="15">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -4418,7 +4414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.5">
+    <row r="24" spans="2:7" ht="15">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -4426,46 +4422,46 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.5">
+    <row r="25" spans="2:7" ht="15">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.5">
+    <row r="26" spans="2:7" ht="15">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.5">
+    <row r="27" spans="2:7" ht="15">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.5">
+    <row r="28" spans="2:7" ht="15">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.5">
+    <row r="29" spans="2:7" ht="15">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.5">
+    <row r="30" spans="2:7" ht="15">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="14.5">
+    <row r="31" spans="2:7" ht="15">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="14.5">
+    <row r="32" spans="2:7" ht="15">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="14.5">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -4477,28 +4473,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.453125" style="11"/>
+    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.5">
+    <row r="1" spans="2:12" ht="12.75">
       <c r="B1" s="6"/>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:12" ht="12.5">
+    <row r="2" spans="2:12" ht="12.75">
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -4509,7 +4505,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="2:12" ht="12.5">
+    <row r="3" spans="2:12" ht="12.75">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4528,7 +4524,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="2:12" ht="12">
+    <row r="5" spans="2:12">
       <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
@@ -4637,7 +4633,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:12" ht="12">
+    <row r="15" spans="2:12">
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
@@ -4685,7 +4681,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.5">
+    <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4696,7 +4692,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="12.5">
+    <row r="19" spans="2:14" ht="12.75">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -4707,7 +4703,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="12.5">
+    <row r="20" spans="2:14" ht="12.75">
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -4718,7 +4714,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="14.5">
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4733,7 +4729,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.5">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4748,7 +4744,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.5">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4763,7 +4759,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.5">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4778,7 +4774,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.5">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4793,7 +4789,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.5">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4808,7 +4804,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.5">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4823,7 +4819,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.5">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4838,7 +4834,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.5">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4853,7 +4849,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.5">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4868,7 +4864,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.5">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4883,7 +4879,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.5">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4898,7 +4894,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.5">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4913,7 +4909,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.5">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4928,7 +4924,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.5">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4943,7 +4939,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.5">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4958,7 +4954,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.5">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4973,7 +4969,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.5">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4988,7 +4984,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.5">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -5003,7 +4999,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.5">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5018,7 +5014,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.5">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5033,7 +5029,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.5">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5058,25 +5054,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.453125" style="11"/>
-    <col min="5" max="5" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="11"/>
+    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="11"/>
-    <col min="12" max="12" width="17.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.453125" style="11"/>
+    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="11"/>
+    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.5" thickBot="1">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -5090,7 +5086,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -5123,7 +5119,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13">
+    <row r="4" spans="1:14" ht="13.5">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -5148,7 +5144,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13">
+    <row r="5" spans="1:14" ht="13.5">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -5175,7 +5171,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13">
+    <row r="6" spans="1:14" ht="13.5">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -5196,7 +5192,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13">
+    <row r="7" spans="1:14" ht="13.5">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -5217,7 +5213,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13">
+    <row r="8" spans="1:14" ht="13.5">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -5244,7 +5240,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13">
+    <row r="9" spans="1:14" ht="13.5">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -5271,7 +5267,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13">
+    <row r="10" spans="1:14" ht="13.5">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -5298,7 +5294,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13">
+    <row r="11" spans="1:14" ht="13.5">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -5325,7 +5321,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13">
+    <row r="12" spans="1:14" ht="13.5">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -5352,7 +5348,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13">
+    <row r="13" spans="1:14" ht="13.5">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -5379,7 +5375,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13">
+    <row r="14" spans="1:14" ht="13.5">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -5406,7 +5402,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13">
+    <row r="15" spans="1:14" ht="13.5">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -5433,7 +5429,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13">
+    <row r="16" spans="1:14" ht="13.5">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -5460,7 +5456,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13">
+    <row r="17" spans="1:14" ht="13.5">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -5487,7 +5483,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13">
+    <row r="18" spans="1:14" ht="13.5">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -5513,7 +5509,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13">
+    <row r="19" spans="1:14" ht="13.5">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -5539,7 +5535,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13">
+    <row r="20" spans="1:14" ht="13.5">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -5565,7 +5561,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13">
+    <row r="21" spans="1:14" ht="13.5">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -5591,7 +5587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13">
+    <row r="22" spans="1:14" ht="13.5">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -5617,7 +5613,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13">
+    <row r="23" spans="1:14" ht="13.5">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5643,7 +5639,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13">
+    <row r="24" spans="1:14" ht="13.5">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -5669,7 +5665,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13">
+    <row r="25" spans="1:14" ht="13.5">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -5695,7 +5691,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13">
+    <row r="26" spans="1:14" ht="13.5">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -5712,7 +5708,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13">
+    <row r="27" spans="1:14" ht="13.5">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -5729,7 +5725,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13">
+    <row r="28" spans="1:14" ht="13.5">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -5746,7 +5742,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13">
+    <row r="29" spans="1:14" ht="13.5">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -5763,7 +5759,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13">
+    <row r="30" spans="1:14" ht="13.5">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -5780,7 +5776,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13">
+    <row r="31" spans="1:14" ht="13.5">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -5797,7 +5793,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13">
+    <row r="32" spans="1:14" ht="13.5">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -5814,7 +5810,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13">
+    <row r="33" spans="2:9" ht="13.5">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -5831,7 +5827,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13">
+    <row r="34" spans="2:9" ht="13.5">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -5848,7 +5844,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13">
+    <row r="35" spans="2:9" ht="13.5">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -5865,7 +5861,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13">
+    <row r="36" spans="2:9" ht="13.5">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -5882,7 +5878,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13">
+    <row r="37" spans="2:9" ht="13.5">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -5899,7 +5895,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13">
+    <row r="38" spans="2:9" ht="13.5">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -5916,7 +5912,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13">
+    <row r="39" spans="2:9" ht="13.5">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -5933,7 +5929,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13">
+    <row r="40" spans="2:9" ht="13.5">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -5950,7 +5946,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13">
+    <row r="41" spans="2:9" ht="13.5">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -5967,7 +5963,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13">
+    <row r="42" spans="2:9" ht="13.5">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -5984,7 +5980,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13">
+    <row r="43" spans="2:9" ht="13.5">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -6001,7 +5997,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13">
+    <row r="44" spans="2:9" ht="13.5">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -6018,7 +6014,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13">
+    <row r="45" spans="2:9" ht="13.5">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -6035,7 +6031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13">
+    <row r="46" spans="2:9" ht="13.5">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -6052,7 +6048,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13">
+    <row r="47" spans="2:9" ht="13.5">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -6069,7 +6065,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13">
+    <row r="48" spans="2:9" ht="13.5">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -6086,7 +6082,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13">
+    <row r="49" spans="2:9" ht="13.5">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -6103,7 +6099,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13">
+    <row r="50" spans="2:9" ht="13.5">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -6120,7 +6116,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13">
+    <row r="51" spans="2:9" ht="13.5">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -6140,7 +6136,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13">
+    <row r="52" spans="2:9" ht="13.5">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -6154,7 +6150,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13">
+    <row r="53" spans="2:9" ht="13.5">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -6168,7 +6164,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13">
+    <row r="54" spans="2:9" ht="13.5">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -6634,12 +6630,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.5" thickBot="1">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>48</v>
       </c>
@@ -6659,7 +6655,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.5">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -6675,7 +6671,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.5">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -6698,19 +6694,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.81640625" style="6"/>
-    <col min="3" max="3" width="20.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.81640625" style="6"/>
+    <col min="1" max="2" width="8.85546875" style="6"/>
+    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.5" thickBot="1">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
@@ -6897,17 +6893,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="13">
+    <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.5" thickBot="1">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40783C0B-64A0-4CE9-82D0-250664437A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D543A72C-41B5-4A95-BC97-55A924E0A464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="16" spans="2:7" ht="15">
       <c r="B16" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>46</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="17" spans="2:7" ht="15">
       <c r="B17" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>46</v>
@@ -4423,7 +4423,9 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="15">
-      <c r="B25" s="9"/>
+      <c r="B25" s="9">
+        <v>10</v>
+      </c>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D543A72C-41B5-4A95-BC97-55A924E0A464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2336CF-EBAE-4FBA-A74D-B7D9394ACBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3220,15 +3220,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3287,19 +3287,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="18" thickBot="1">
+    <row r="3" spans="2:18" ht="17.5" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -4195,15 +4195,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="6"/>
-    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="9.1796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="6"/>
+    <col min="4" max="4" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.453125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4234,7 +4234,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15">
+    <row r="12" spans="2:7" ht="14.5">
       <c r="B12" s="7" t="s">
         <v>276</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15">
+    <row r="13" spans="2:7" ht="14.5">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15">
+    <row r="14" spans="2:7" ht="14.5">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15">
+    <row r="15" spans="2:7" ht="14.5">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15">
+    <row r="16" spans="2:7" ht="14.5">
       <c r="B16" s="9">
         <v>5</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15">
+    <row r="17" spans="2:7" ht="14.5">
       <c r="B17" s="9">
         <v>5</v>
       </c>
@@ -4342,9 +4342,9 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15">
+    <row r="18" spans="2:7" ht="14.5">
       <c r="B18" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>46</v>
@@ -4362,9 +4362,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15">
+    <row r="19" spans="2:7" ht="14.5">
       <c r="B19" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>46</v>
@@ -4378,10 +4378,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15">
-      <c r="B20" s="9">
-        <v>10</v>
-      </c>
+    <row r="20" spans="2:7" ht="14.5">
+      <c r="B20" s="9"/>
       <c r="D20" s="6" t="s">
         <v>46</v>
       </c>
@@ -4390,80 +4388,70 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15">
-      <c r="B21" s="9">
-        <v>10</v>
-      </c>
+    <row r="21" spans="2:7" ht="14.5">
+      <c r="B21" s="9"/>
       <c r="D21" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15">
-      <c r="B22" s="9">
-        <v>10</v>
-      </c>
+    <row r="22" spans="2:7" ht="14.5">
+      <c r="B22" s="9"/>
       <c r="D22" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15">
-      <c r="B23" s="9">
-        <v>10</v>
-      </c>
+    <row r="23" spans="2:7" ht="14.5">
+      <c r="B23" s="9"/>
       <c r="D23" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15">
-      <c r="B24" s="9">
-        <v>10</v>
-      </c>
+    <row r="24" spans="2:7" ht="14.5">
+      <c r="B24" s="9"/>
       <c r="D24" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15">
-      <c r="B25" s="9">
-        <v>10</v>
-      </c>
+    <row r="25" spans="2:7" ht="14.5">
+      <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15">
+    <row r="26" spans="2:7" ht="14.5">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15">
+    <row r="27" spans="2:7" ht="14.5">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15">
+    <row r="28" spans="2:7" ht="14.5">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="15">
+    <row r="29" spans="2:7" ht="14.5">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="15">
+    <row r="30" spans="2:7" ht="14.5">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="15">
+    <row r="31" spans="2:7" ht="14.5">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="15">
+    <row r="32" spans="2:7" ht="14.5">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" spans="2:2" ht="14.5">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -4475,28 +4463,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="11"/>
+    <col min="2" max="2" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="11"/>
+    <col min="9" max="9" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.453125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
+    <row r="1" spans="2:12" ht="12.5">
       <c r="B1" s="6"/>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:12" ht="12.75">
+    <row r="2" spans="2:12" ht="12.5">
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -4507,7 +4495,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="2:12" ht="12.75">
+    <row r="3" spans="2:12" ht="12.5">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4526,7 +4514,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" ht="12">
       <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
@@ -4635,7 +4623,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" ht="12">
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
@@ -4683,7 +4671,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.75">
+    <row r="18" spans="2:14" ht="12.5">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4694,7 +4682,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="12.75">
+    <row r="19" spans="2:14" ht="12.5">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -4705,7 +4693,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="12.75">
+    <row r="20" spans="2:14" ht="12.5">
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -4716,7 +4704,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
+    <row r="21" spans="2:14" ht="14.5">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4731,7 +4719,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="15">
+    <row r="22" spans="2:14" ht="14.5">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4746,7 +4734,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="15">
+    <row r="23" spans="2:14" ht="14.5">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4761,7 +4749,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="15">
+    <row r="24" spans="2:14" ht="14.5">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4776,7 +4764,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="15">
+    <row r="25" spans="2:14" ht="14.5">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4791,7 +4779,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="15">
+    <row r="26" spans="2:14" ht="14.5">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4806,7 +4794,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="15">
+    <row r="27" spans="2:14" ht="14.5">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4821,7 +4809,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="15">
+    <row r="28" spans="2:14" ht="14.5">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4836,7 +4824,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="15">
+    <row r="29" spans="2:14" ht="14.5">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4851,7 +4839,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="15">
+    <row r="30" spans="2:14" ht="14.5">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4866,7 +4854,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="15">
+    <row r="31" spans="2:14" ht="14.5">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4881,7 +4869,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="15">
+    <row r="32" spans="2:14" ht="14.5">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4896,7 +4884,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="15">
+    <row r="33" spans="2:14" ht="14.5">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4911,7 +4899,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="15">
+    <row r="34" spans="2:14" ht="14.5">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4926,7 +4914,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="15">
+    <row r="35" spans="2:14" ht="14.5">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4941,7 +4929,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="15">
+    <row r="36" spans="2:14" ht="14.5">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4956,7 +4944,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="15">
+    <row r="37" spans="2:14" ht="14.5">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4971,7 +4959,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="15">
+    <row r="38" spans="2:14" ht="14.5">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4986,7 +4974,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="15">
+    <row r="39" spans="2:14" ht="14.5">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -5001,7 +4989,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="15">
+    <row r="40" spans="2:14" ht="14.5">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5016,7 +5004,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="15">
+    <row r="41" spans="2:14" ht="14.5">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5031,7 +5019,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="15">
+    <row r="42" spans="2:14" ht="14.5">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5056,25 +5044,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="11"/>
-    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="11"/>
+    <col min="2" max="2" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" style="11"/>
+    <col min="5" max="5" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="11"/>
-    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="11"/>
+    <col min="10" max="10" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" style="11"/>
+    <col min="12" max="12" width="17.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.453125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="18" thickBot="1">
+    <row r="2" spans="1:14" ht="17.5" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -5088,7 +5076,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -5121,7 +5109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -5146,7 +5134,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -5173,7 +5161,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -5194,7 +5182,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -5215,7 +5203,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -5242,7 +5230,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -5269,7 +5257,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -5296,7 +5284,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -5323,7 +5311,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -5350,7 +5338,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -5377,7 +5365,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -5404,7 +5392,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -5431,7 +5419,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -5458,7 +5446,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -5485,7 +5473,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -5511,7 +5499,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -5537,7 +5525,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -5563,7 +5551,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -5589,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -5615,7 +5603,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5641,7 +5629,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -5667,7 +5655,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -5693,7 +5681,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -5710,7 +5698,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -5727,7 +5715,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -5744,7 +5732,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.5">
+    <row r="29" spans="1:14" ht="13">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -5761,7 +5749,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.5">
+    <row r="30" spans="1:14" ht="13">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -5778,7 +5766,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.5">
+    <row r="31" spans="1:14" ht="13">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -5795,7 +5783,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.5">
+    <row r="32" spans="1:14" ht="13">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -5812,7 +5800,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.5">
+    <row r="33" spans="2:9" ht="13">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -5829,7 +5817,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5">
+    <row r="34" spans="2:9" ht="13">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -5846,7 +5834,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5">
+    <row r="35" spans="2:9" ht="13">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -5863,7 +5851,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.5">
+    <row r="36" spans="2:9" ht="13">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -5880,7 +5868,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.5">
+    <row r="37" spans="2:9" ht="13">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -5897,7 +5885,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.5">
+    <row r="38" spans="2:9" ht="13">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -5914,7 +5902,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5">
+    <row r="39" spans="2:9" ht="13">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -5931,7 +5919,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.5">
+    <row r="40" spans="2:9" ht="13">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -5948,7 +5936,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.5">
+    <row r="41" spans="2:9" ht="13">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -5965,7 +5953,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.5">
+    <row r="42" spans="2:9" ht="13">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -5982,7 +5970,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.5">
+    <row r="43" spans="2:9" ht="13">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -5999,7 +5987,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.5">
+    <row r="44" spans="2:9" ht="13">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -6016,7 +6004,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.5">
+    <row r="45" spans="2:9" ht="13">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -6033,7 +6021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.5">
+    <row r="46" spans="2:9" ht="13">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -6050,7 +6038,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.5">
+    <row r="47" spans="2:9" ht="13">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -6067,7 +6055,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.5">
+    <row r="48" spans="2:9" ht="13">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -6084,7 +6072,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.5">
+    <row r="49" spans="2:9" ht="13">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -6101,7 +6089,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.5">
+    <row r="50" spans="2:9" ht="13">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -6118,7 +6106,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.5">
+    <row r="51" spans="2:9" ht="13">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -6138,7 +6126,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.5">
+    <row r="52" spans="2:9" ht="13">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -6152,7 +6140,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.5">
+    <row r="53" spans="2:9" ht="13">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -6166,7 +6154,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.5">
+    <row r="54" spans="2:9" ht="13">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -6632,12 +6620,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="18" thickBot="1">
+    <row r="99" spans="5:10" ht="17.5" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>48</v>
       </c>
@@ -6657,7 +6645,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="15">
+    <row r="101" spans="5:10" ht="14.5">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -6673,7 +6661,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="15">
+    <row r="102" spans="5:10" ht="14.5">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -6696,19 +6684,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="6"/>
-    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="2" width="8.81640625" style="6"/>
+    <col min="3" max="3" width="20.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18" thickBot="1">
+    <row r="3" spans="2:4" ht="17.5" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
@@ -6895,17 +6883,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" ht="13">
       <c r="B23" s="18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="18" thickBot="1">
+    <row r="25" spans="2:4" ht="17.5" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2336CF-EBAE-4FBA-A74D-B7D9394ACBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B02C61-5D1A-46DD-BEF8-37FE820AB6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="281">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,6 +869,18 @@
   </si>
   <si>
     <t>PDef1</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>diesel</t>
+  </si>
+  <si>
+    <t>kerosene</t>
+  </si>
+  <si>
+    <t>gasoline</t>
   </si>
 </sst>
 </file>
@@ -3297,6 +3309,9 @@
     <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:18" ht="17.5" thickBot="1">
@@ -3454,7 +3469,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -3483,7 +3498,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -3512,7 +3527,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
@@ -3541,7 +3556,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -3570,7 +3585,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -3599,10 +3614,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
       </c>
       <c r="M13" t="s">
         <v>17</v>
@@ -3628,10 +3652,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D14" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -3660,10 +3681,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -3692,23 +3710,11 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
       <c r="M16" t="s">
         <v>17</v>
       </c>
@@ -3730,13 +3736,10 @@
     </row>
     <row r="17" spans="2:18">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -3762,17 +3765,23 @@
     </row>
     <row r="18" spans="2:18">
       <c r="B18" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
       </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
       <c r="M18" t="s">
         <v>17</v>
       </c>
@@ -3794,13 +3803,13 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -3826,13 +3835,13 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3858,23 +3867,17 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D21" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>25</v>
-      </c>
       <c r="M21" t="s">
         <v>17</v>
       </c>
@@ -3896,16 +3899,16 @@
     </row>
     <row r="22" spans="2:18">
       <c r="B22" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="M22" t="s">
         <v>17</v>
@@ -3928,13 +3931,16 @@
     </row>
     <row r="23" spans="2:18">
       <c r="B23" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="M23" t="s">
         <v>17</v>
@@ -3957,13 +3963,16 @@
     </row>
     <row r="24" spans="2:18">
       <c r="B24" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="M24" t="s">
         <v>17</v>
@@ -3985,6 +3994,18 @@
       </c>
     </row>
     <row r="25" spans="2:18">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
       <c r="M25" t="s">
         <v>17</v>
       </c>
@@ -4005,6 +4026,18 @@
       </c>
     </row>
     <row r="26" spans="2:18">
+      <c r="B26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>195</v>
+      </c>
       <c r="M26" t="s">
         <v>17</v>
       </c>
@@ -4025,6 +4058,15 @@
       </c>
     </row>
     <row r="27" spans="2:18">
+      <c r="B27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" t="s">
+        <v>195</v>
+      </c>
       <c r="M27" t="s">
         <v>17</v>
       </c>
@@ -4045,6 +4087,15 @@
       </c>
     </row>
     <row r="28" spans="2:18">
+      <c r="B28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" t="s">
+        <v>195</v>
+      </c>
       <c r="M28" t="s">
         <v>17</v>
       </c>
@@ -4185,8 +4236,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C334">
-    <sortCondition ref="C19:C334"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C12:C338">
+    <sortCondition ref="C23:C338"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B02C61-5D1A-46DD-BEF8-37FE820AB6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717E5AEC-F1E9-4A08-84A6-45EAE2A9EE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="281">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -3231,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H5"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>7</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
         <v>212</v>
@@ -3288,6 +3288,14 @@
       </c>
       <c r="H5" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD363E32-34CE-41BF-A6D9-514B0BD81125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8D6E4D-81E7-485E-8BC6-C911483505CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="277">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,9 +869,6 @@
   </si>
   <si>
     <t>PDef1</t>
-  </si>
-  <si>
-    <t>LVA</t>
   </si>
 </sst>
 </file>
@@ -3221,15 +3218,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3272,9 +3269,6 @@
       </c>
     </row>
     <row r="5" spans="2:8">
-      <c r="C5" t="s">
-        <v>277</v>
-      </c>
       <c r="F5" t="s">
         <v>37</v>
       </c>
@@ -3291,19 +3285,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.5" thickBot="1">
+    <row r="3" spans="2:18" ht="18" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3322,7 +3316,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -4199,15 +4193,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="6"/>
-    <col min="4" max="4" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="6"/>
+    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="6"/>
+    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4238,7 +4232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.5">
+    <row r="12" spans="2:7" ht="15">
       <c r="B12" s="7" t="s">
         <v>276</v>
       </c>
@@ -4258,7 +4252,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.5">
+    <row r="13" spans="2:7" ht="15">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -4266,7 +4260,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.5">
+    <row r="14" spans="2:7" ht="15">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -4286,7 +4280,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.5">
+    <row r="15" spans="2:7" ht="15">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -4306,7 +4300,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.5">
+    <row r="16" spans="2:7" ht="15">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -4326,7 +4320,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.5">
+    <row r="17" spans="2:7" ht="15">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -4346,7 +4340,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.5">
+    <row r="18" spans="2:7" ht="15">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -4366,7 +4360,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.5">
+    <row r="19" spans="2:7" ht="15">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -4382,7 +4376,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.5">
+    <row r="20" spans="2:7" ht="15">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -4394,7 +4388,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.5">
+    <row r="21" spans="2:7" ht="15">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -4402,7 +4396,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.5">
+    <row r="22" spans="2:7" ht="15">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -4410,7 +4404,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.5">
+    <row r="23" spans="2:7" ht="15">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -4418,7 +4412,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.5">
+    <row r="24" spans="2:7" ht="15">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -4426,46 +4420,46 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.5">
+    <row r="25" spans="2:7" ht="15">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.5">
+    <row r="26" spans="2:7" ht="15">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.5">
+    <row r="27" spans="2:7" ht="15">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.5">
+    <row r="28" spans="2:7" ht="15">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.5">
+    <row r="29" spans="2:7" ht="15">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.5">
+    <row r="30" spans="2:7" ht="15">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="14.5">
+    <row r="31" spans="2:7" ht="15">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="14.5">
+    <row r="32" spans="2:7" ht="15">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="14.5">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -4477,28 +4471,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.453125" style="11"/>
+    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.5">
+    <row r="1" spans="2:12" ht="12.75">
       <c r="B1" s="6"/>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:12" ht="12.5">
+    <row r="2" spans="2:12" ht="12.75">
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -4509,7 +4503,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="2:12" ht="12.5">
+    <row r="3" spans="2:12" ht="12.75">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4528,7 +4522,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="2:12" ht="12">
+    <row r="5" spans="2:12">
       <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
@@ -4637,7 +4631,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:12" ht="12">
+    <row r="15" spans="2:12">
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
@@ -4685,7 +4679,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.5">
+    <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4696,7 +4690,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="12.5">
+    <row r="19" spans="2:14" ht="12.75">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -4707,7 +4701,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="12.5">
+    <row r="20" spans="2:14" ht="12.75">
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -4718,7 +4712,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="14.5">
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4733,7 +4727,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.5">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4748,7 +4742,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.5">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4763,7 +4757,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.5">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4778,7 +4772,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.5">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4793,7 +4787,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.5">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4808,7 +4802,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.5">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4823,7 +4817,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.5">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4838,7 +4832,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.5">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4853,7 +4847,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.5">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4868,7 +4862,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.5">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4883,7 +4877,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.5">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4898,7 +4892,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.5">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4913,7 +4907,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.5">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4928,7 +4922,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.5">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4943,7 +4937,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.5">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4958,7 +4952,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.5">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4973,7 +4967,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.5">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4988,7 +4982,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.5">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -5003,7 +4997,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.5">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5018,7 +5012,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.5">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5033,7 +5027,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.5">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5058,25 +5052,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.453125" style="11"/>
-    <col min="5" max="5" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="11"/>
+    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="11"/>
-    <col min="12" max="12" width="17.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.453125" style="11"/>
+    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="11"/>
+    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.5" thickBot="1">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -5090,7 +5084,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -5123,7 +5117,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13">
+    <row r="4" spans="1:14" ht="13.5">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -5148,7 +5142,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13">
+    <row r="5" spans="1:14" ht="13.5">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -5175,7 +5169,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13">
+    <row r="6" spans="1:14" ht="13.5">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -5196,7 +5190,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13">
+    <row r="7" spans="1:14" ht="13.5">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -5217,7 +5211,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13">
+    <row r="8" spans="1:14" ht="13.5">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -5244,7 +5238,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13">
+    <row r="9" spans="1:14" ht="13.5">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -5271,7 +5265,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13">
+    <row r="10" spans="1:14" ht="13.5">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -5298,7 +5292,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13">
+    <row r="11" spans="1:14" ht="13.5">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -5325,7 +5319,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13">
+    <row r="12" spans="1:14" ht="13.5">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -5352,7 +5346,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13">
+    <row r="13" spans="1:14" ht="13.5">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -5379,7 +5373,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13">
+    <row r="14" spans="1:14" ht="13.5">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -5406,7 +5400,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13">
+    <row r="15" spans="1:14" ht="13.5">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -5433,7 +5427,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13">
+    <row r="16" spans="1:14" ht="13.5">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -5460,7 +5454,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13">
+    <row r="17" spans="1:14" ht="13.5">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -5487,7 +5481,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13">
+    <row r="18" spans="1:14" ht="13.5">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -5513,7 +5507,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13">
+    <row r="19" spans="1:14" ht="13.5">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -5539,7 +5533,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13">
+    <row r="20" spans="1:14" ht="13.5">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -5565,7 +5559,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13">
+    <row r="21" spans="1:14" ht="13.5">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -5591,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13">
+    <row r="22" spans="1:14" ht="13.5">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -5617,7 +5611,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13">
+    <row r="23" spans="1:14" ht="13.5">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5643,7 +5637,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13">
+    <row r="24" spans="1:14" ht="13.5">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -5669,7 +5663,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13">
+    <row r="25" spans="1:14" ht="13.5">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -5695,7 +5689,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13">
+    <row r="26" spans="1:14" ht="13.5">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -5712,7 +5706,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13">
+    <row r="27" spans="1:14" ht="13.5">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -5729,7 +5723,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13">
+    <row r="28" spans="1:14" ht="13.5">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -5746,7 +5740,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13">
+    <row r="29" spans="1:14" ht="13.5">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -5763,7 +5757,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13">
+    <row r="30" spans="1:14" ht="13.5">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -5780,7 +5774,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13">
+    <row r="31" spans="1:14" ht="13.5">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -5797,7 +5791,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13">
+    <row r="32" spans="1:14" ht="13.5">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -5814,7 +5808,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13">
+    <row r="33" spans="2:9" ht="13.5">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -5831,7 +5825,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13">
+    <row r="34" spans="2:9" ht="13.5">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -5848,7 +5842,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13">
+    <row r="35" spans="2:9" ht="13.5">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -5865,7 +5859,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13">
+    <row r="36" spans="2:9" ht="13.5">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -5882,7 +5876,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13">
+    <row r="37" spans="2:9" ht="13.5">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -5899,7 +5893,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13">
+    <row r="38" spans="2:9" ht="13.5">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -5916,7 +5910,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13">
+    <row r="39" spans="2:9" ht="13.5">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -5933,7 +5927,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13">
+    <row r="40" spans="2:9" ht="13.5">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -5950,7 +5944,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13">
+    <row r="41" spans="2:9" ht="13.5">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -5967,7 +5961,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13">
+    <row r="42" spans="2:9" ht="13.5">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -5984,7 +5978,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13">
+    <row r="43" spans="2:9" ht="13.5">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -6001,7 +5995,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13">
+    <row r="44" spans="2:9" ht="13.5">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -6018,7 +6012,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13">
+    <row r="45" spans="2:9" ht="13.5">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -6035,7 +6029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13">
+    <row r="46" spans="2:9" ht="13.5">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -6052,7 +6046,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13">
+    <row r="47" spans="2:9" ht="13.5">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -6069,7 +6063,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13">
+    <row r="48" spans="2:9" ht="13.5">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -6086,7 +6080,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13">
+    <row r="49" spans="2:9" ht="13.5">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -6103,7 +6097,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13">
+    <row r="50" spans="2:9" ht="13.5">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -6120,7 +6114,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13">
+    <row r="51" spans="2:9" ht="13.5">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -6140,7 +6134,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13">
+    <row r="52" spans="2:9" ht="13.5">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -6154,7 +6148,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13">
+    <row r="53" spans="2:9" ht="13.5">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -6168,7 +6162,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13">
+    <row r="54" spans="2:9" ht="13.5">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -6634,12 +6628,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.5" thickBot="1">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>48</v>
       </c>
@@ -6659,7 +6653,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.5">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -6675,7 +6669,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.5">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -6698,19 +6692,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.81640625" style="6"/>
-    <col min="3" max="3" width="20.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.81640625" style="6"/>
+    <col min="1" max="2" width="8.85546875" style="6"/>
+    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.5" thickBot="1">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
@@ -6897,17 +6891,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="13">
+    <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.5" thickBot="1">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717E5AEC-F1E9-4A08-84A6-45EAE2A9EE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1E127-73C2-4AAB-BC92-02A55278D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="277">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,18 +869,6 @@
   </si>
   <si>
     <t>PDef1</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>diesel</t>
-  </si>
-  <si>
-    <t>kerosene</t>
-  </si>
-  <si>
-    <t>gasoline</t>
   </si>
 </sst>
 </file>
@@ -904,7 +892,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
     <numFmt numFmtId="178" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1281,6 +1269,10 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="47">
@@ -1805,7 +1797,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="437">
+  <cellStyleXfs count="438">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2355,14 +2347,11 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="431"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="22" xfId="432" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="432" applyBorder="1"/>
@@ -2382,8 +2371,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="234"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="234" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="437">
+  <cellStyles count="438">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{822ECCD2-03B4-4EB0-AADE-6DECEB39BB19}"/>
     <cellStyle name="20% - Accent1 3" xfId="5" xr:uid="{58CA3325-8B37-45C5-A177-73E6AEE43B64}"/>
     <cellStyle name="20% - Accent2 2" xfId="6" xr:uid="{3C5AA3C1-DAA0-472F-BECC-C64D10D55099}"/>
@@ -2727,6 +2722,7 @@
     <cellStyle name="Normal 4 7" xfId="333" xr:uid="{FB3CAB90-D8D4-4905-B1F9-E032DC36C5E9}"/>
     <cellStyle name="Normal 4 8" xfId="334" xr:uid="{24133808-68DF-4019-8093-E6DC03171A5E}"/>
     <cellStyle name="Normal 40" xfId="431" xr:uid="{4529572A-9F71-4D31-A9DC-B222CD542D69}"/>
+    <cellStyle name="Normal 40 2" xfId="437" xr:uid="{5B3315BB-D69E-4BFE-8495-7B35572ADC6C}"/>
     <cellStyle name="Normal 5" xfId="335" xr:uid="{C8D3CF72-F067-4EEE-A198-FD4AB132962B}"/>
     <cellStyle name="Normal 5 2" xfId="336" xr:uid="{732DD9CE-11E6-4E2F-A66F-A09233BA7453}"/>
     <cellStyle name="Normal 5 2 2" xfId="337" xr:uid="{186AF356-6A52-4CD3-9443-D570BC418A36}"/>
@@ -3232,15 +3228,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3307,939 +3303,1144 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.5" thickBot="1">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:18" ht="18" thickBot="1">
+      <c r="B3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="M3" s="3" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B4" s="5" t="s">
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="19"/>
+    </row>
+    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:18">
-      <c r="B5" t="s">
+      <c r="B5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M5" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" t="s">
+      <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M6" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:18">
-      <c r="B7" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="19"/>
+      <c r="E7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M7" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" t="s">
+      <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M8" t="s">
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" t="s">
+      <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>279</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M9" t="s">
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" t="s">
+      <c r="B10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M10" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" t="s">
+      <c r="B11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M11" t="s">
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" t="s">
+      <c r="B12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C12" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M12" t="s">
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" t="s">
+      <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C13" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G13" t="s">
+      <c r="R13" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I13" t="s">
+      <c r="Q14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="B15" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="B16" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M13" t="s">
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N13" t="s">
-        <v>231</v>
-      </c>
-      <c r="O13" t="s">
-        <v>232</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="N16" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="Q16" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R16" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="2:18">
-      <c r="B14" t="s">
+    <row r="17" spans="2:18">
+      <c r="B17" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="N17" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
+      <c r="B18" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M14" t="s">
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N14" t="s">
-        <v>233</v>
-      </c>
-      <c r="O14" t="s">
-        <v>234</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="N18" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="Q18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R14" t="s">
+      <c r="R18" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="2:18">
-      <c r="B15" t="s">
+    <row r="19" spans="2:18">
+      <c r="B19" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="N19" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
+      <c r="B20" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M15" t="s">
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N15" t="s">
-        <v>235</v>
-      </c>
-      <c r="O15" t="s">
-        <v>236</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="N20" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q20" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R20" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="2:18">
-      <c r="B16" t="s">
+    <row r="21" spans="2:18">
+      <c r="B21" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C21" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M16" t="s">
+      <c r="F21" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N16" t="s">
-        <v>237</v>
-      </c>
-      <c r="O16" t="s">
-        <v>238</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="N21" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q21" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R16" t="s">
+      <c r="R21" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="17" spans="2:18">
-      <c r="B17" t="s">
+    <row r="22" spans="2:18">
+      <c r="B22" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="N22" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
+      <c r="B23" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N17" t="s">
-        <v>239</v>
-      </c>
-      <c r="O17" t="s">
-        <v>240</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="N23" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q23" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R17" t="s">
+      <c r="R23" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="2:18">
-      <c r="B18" t="s">
+    <row r="24" spans="2:18">
+      <c r="B24" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" t="s">
-        <v>206</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="N24" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G18" t="s">
+      <c r="R24" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="P25" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="M18" t="s">
+      <c r="Q25" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N18" t="s">
-        <v>241</v>
-      </c>
-      <c r="O18" t="s">
-        <v>242</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="N26" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q26" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R18" t="s">
+      <c r="R26" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="19" spans="2:18">
-      <c r="B19" t="s">
+    <row r="27" spans="2:18">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="N27" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="P27" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N19" t="s">
-        <v>243</v>
-      </c>
-      <c r="O19" t="s">
-        <v>244</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="N28" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="P28" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q28" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R28" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="2:18">
-      <c r="B20" t="s">
+    <row r="29" spans="2:18">
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="s">
+      <c r="N29" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="P29" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
+      <c r="Q29" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N20" t="s">
-        <v>245</v>
-      </c>
-      <c r="O20" t="s">
-        <v>246</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="N30" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="P30" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q30" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R30" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="2:18">
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>202</v>
-      </c>
-      <c r="D21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
+    <row r="31" spans="2:18">
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N21" t="s">
-        <v>247</v>
-      </c>
-      <c r="O21" t="s">
-        <v>248</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="N31" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="P31" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R21" t="s">
+      <c r="R31" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="22" spans="2:18">
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
+    <row r="32" spans="2:18">
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N22" t="s">
-        <v>249</v>
-      </c>
-      <c r="O22" t="s">
-        <v>250</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="N32" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="P32" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q32" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R22" t="s">
+      <c r="R32" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="2:18">
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" t="s">
+    <row r="33" spans="13:18">
+      <c r="M33" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N23" t="s">
-        <v>251</v>
-      </c>
-      <c r="O23" t="s">
-        <v>252</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="N33" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q33" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R23" t="s">
+      <c r="R33" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="2:18">
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M24" t="s">
+    <row r="34" spans="13:18">
+      <c r="M34" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="N24" t="s">
-        <v>253</v>
-      </c>
-      <c r="O24" t="s">
-        <v>254</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="N34" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q34" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18">
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M25" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" t="s">
-        <v>255</v>
-      </c>
-      <c r="O25" t="s">
-        <v>256</v>
-      </c>
-      <c r="P25" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>35</v>
-      </c>
-      <c r="R25" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18">
-      <c r="B26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E26" t="s">
-        <v>195</v>
-      </c>
-      <c r="M26" t="s">
-        <v>17</v>
-      </c>
-      <c r="N26" t="s">
-        <v>257</v>
-      </c>
-      <c r="O26" t="s">
-        <v>258</v>
-      </c>
-      <c r="P26" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18">
-      <c r="B27" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" t="s">
-        <v>199</v>
-      </c>
-      <c r="E27" t="s">
-        <v>195</v>
-      </c>
-      <c r="M27" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" t="s">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s">
-        <v>260</v>
-      </c>
-      <c r="P27" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>35</v>
-      </c>
-      <c r="R27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="B28" t="s">
-        <v>192</v>
-      </c>
-      <c r="C28" t="s">
-        <v>200</v>
-      </c>
-      <c r="E28" t="s">
-        <v>195</v>
-      </c>
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>261</v>
-      </c>
-      <c r="O28" t="s">
-        <v>262</v>
-      </c>
-      <c r="P28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>263</v>
-      </c>
-      <c r="O29" t="s">
-        <v>264</v>
-      </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="M30" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" t="s">
-        <v>265</v>
-      </c>
-      <c r="O30" t="s">
-        <v>266</v>
-      </c>
-      <c r="P30" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>35</v>
-      </c>
-      <c r="R30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18">
-      <c r="M31" t="s">
-        <v>17</v>
-      </c>
-      <c r="N31" t="s">
-        <v>267</v>
-      </c>
-      <c r="O31" t="s">
-        <v>268</v>
-      </c>
-      <c r="P31" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>35</v>
-      </c>
-      <c r="R31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18">
-      <c r="M32" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" t="s">
-        <v>269</v>
-      </c>
-      <c r="O32" t="s">
-        <v>270</v>
-      </c>
-      <c r="P32" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="13:18">
-      <c r="M33" t="s">
-        <v>17</v>
-      </c>
-      <c r="N33" t="s">
-        <v>271</v>
-      </c>
-      <c r="O33" t="s">
-        <v>272</v>
-      </c>
-      <c r="P33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="13:18">
-      <c r="M34" t="s">
-        <v>17</v>
-      </c>
-      <c r="N34" t="s">
-        <v>273</v>
-      </c>
-      <c r="O34" t="s">
-        <v>274</v>
-      </c>
-      <c r="P34" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="R34" s="19" t="s">
         <v>216</v>
       </c>
     </row>
@@ -4254,264 +4455,264 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="6"/>
-    <col min="4" max="4" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="6"/>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="2"/>
+    <col min="4" max="4" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:7">
-      <c r="B4" s="6">
+      <c r="B4" s="2">
         <v>2022</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.5">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="2:7" ht="15">
+      <c r="B12" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="8" t="str">
+      <c r="E12" s="4" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
         <v>msy7_2050</v>
       </c>
-      <c r="F12" s="8" t="str">
+      <c r="F12" s="4" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
         <v>msy6_2050</v>
       </c>
-      <c r="G12" s="8" t="str">
+      <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.5">
-      <c r="B13" s="9">
+    <row r="13" spans="2:7" ht="15">
+      <c r="B13" s="5">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.5">
-      <c r="B14" s="9">
+    <row r="14" spans="2:7" ht="15">
+      <c r="B14" s="5">
         <v>5</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="2">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
         <v>2022</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <f t="shared" si="1"/>
         <v>2022</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="2">
         <f t="shared" si="1"/>
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.5">
-      <c r="B15" s="9">
+    <row r="15" spans="2:7" ht="15">
+      <c r="B15" s="5">
         <v>5</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="2">
         <f>E14+3</f>
         <v>2025</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <f>F14+3</f>
         <v>2025</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="2">
         <f>G14+3</f>
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.5">
-      <c r="B16" s="9">
+    <row r="16" spans="2:7" ht="15">
+      <c r="B16" s="5">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="2">
         <f>E15+5</f>
         <v>2030</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="2">
         <f>F15+5</f>
         <v>2030</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="2">
         <f>G15+5</f>
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.5">
-      <c r="B17" s="9">
+    <row r="17" spans="2:7" ht="15">
+      <c r="B17" s="5">
         <v>5</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="2">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
         <v>2035</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="2">
         <f>F16+5</f>
         <v>2035</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="2">
         <f>G16+10</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.5">
-      <c r="B18" s="9">
+    <row r="18" spans="2:7" ht="15">
+      <c r="B18" s="5">
         <v>5</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="2">
         <f t="shared" si="2"/>
         <v>2040</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="2">
         <f>F17+5</f>
         <v>2040</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="2">
         <f t="shared" ref="G18" si="3">G17+10</f>
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.5">
-      <c r="B19" s="9">
+    <row r="19" spans="2:7" ht="15">
+      <c r="B19" s="5">
         <v>5</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="2">
         <f t="shared" si="2"/>
         <v>2045</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="2">
         <f>F18+10</f>
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.5">
-      <c r="B20" s="9"/>
-      <c r="D20" s="6" t="s">
+    <row r="20" spans="2:7" ht="15">
+      <c r="B20" s="5"/>
+      <c r="D20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="2">
         <f t="shared" si="2"/>
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.5">
-      <c r="B21" s="9"/>
-      <c r="D21" s="6" t="s">
+    <row r="21" spans="2:7" ht="15">
+      <c r="B21" s="5"/>
+      <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.5">
-      <c r="B22" s="9"/>
-      <c r="D22" s="6" t="s">
+    <row r="22" spans="2:7" ht="15">
+      <c r="B22" s="5"/>
+      <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.5">
-      <c r="B23" s="9"/>
-      <c r="D23" s="6" t="s">
+    <row r="23" spans="2:7" ht="15">
+      <c r="B23" s="5"/>
+      <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.5">
-      <c r="B24" s="9"/>
-      <c r="D24" s="6" t="s">
+    <row r="24" spans="2:7" ht="15">
+      <c r="B24" s="5"/>
+      <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.5">
-      <c r="B25" s="9"/>
-      <c r="D25" s="6" t="s">
+    <row r="25" spans="2:7" ht="15">
+      <c r="B25" s="5"/>
+      <c r="D25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.5">
-      <c r="B26" s="9"/>
-      <c r="D26" s="6" t="s">
+    <row r="26" spans="2:7" ht="15">
+      <c r="B26" s="5"/>
+      <c r="D26" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.5">
-      <c r="B27" s="9"/>
-      <c r="D27" s="6" t="s">
+    <row r="27" spans="2:7" ht="15">
+      <c r="B27" s="5"/>
+      <c r="D27" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.5">
-      <c r="B28" s="9"/>
-      <c r="D28" s="6" t="s">
+    <row r="28" spans="2:7" ht="15">
+      <c r="B28" s="5"/>
+      <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.5">
-      <c r="B29" s="9"/>
-      <c r="D29" s="6" t="s">
+    <row r="29" spans="2:7" ht="15">
+      <c r="B29" s="5"/>
+      <c r="D29" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.5">
-      <c r="B30" s="9"/>
-    </row>
-    <row r="31" spans="2:7" ht="14.5">
-      <c r="B31" s="9"/>
-    </row>
-    <row r="32" spans="2:7" ht="14.5">
-      <c r="B32" s="9"/>
-    </row>
-    <row r="33" spans="2:2" ht="14.5">
-      <c r="B33" s="9"/>
+    <row r="30" spans="2:7" ht="15">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="2:7" ht="15">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="2:7" ht="15">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" ht="15">
+      <c r="B33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4522,248 +4723,248 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.453125" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="2" max="2" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.5">
-      <c r="B1" s="6"/>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="2:12" ht="12.5">
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="2:12" ht="12.5">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+    <row r="1" spans="2:12" ht="12.75">
+      <c r="B1" s="2"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="2:12" ht="12.75">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="2:12" ht="12.75">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="2:12" ht="12">
-      <c r="B5" s="15" t="s">
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="7">
         <v>0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="7">
         <v>0</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="7">
         <v>0</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="7">
         <v>0</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="7">
         <v>0</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="7">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="2:12" ht="12">
-      <c r="B15" s="15" t="s">
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="7">
         <v>2222</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:14">
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="7">
         <v>8888</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.5">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-    </row>
-    <row r="19" spans="2:14" ht="12.5">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="2:14" ht="12.5">
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="2:14" ht="14.5">
+    <row r="18" spans="2:14" ht="12.75">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="2:14" ht="12.75">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4778,7 +4979,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.5">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4793,7 +4994,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.5">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4808,7 +5009,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.5">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4823,7 +5024,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.5">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4838,7 +5039,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.5">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4853,7 +5054,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.5">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4868,7 +5069,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.5">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4883,7 +5084,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.5">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4898,7 +5099,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.5">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4913,7 +5114,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.5">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4928,7 +5129,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.5">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4943,7 +5144,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.5">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4958,7 +5159,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.5">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4973,7 +5174,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.5">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4988,7 +5189,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.5">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -5003,7 +5204,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.5">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -5018,7 +5219,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.5">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -5033,7 +5234,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.5">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -5048,7 +5249,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.5">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5063,7 +5264,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.5">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5078,7 +5279,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.5">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5103,1633 +5304,1633 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11"/>
-    <col min="2" max="2" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.453125" style="11"/>
-    <col min="5" max="5" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="11"/>
-    <col min="12" max="12" width="17.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.453125" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="2" max="2" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="7"/>
+    <col min="5" max="5" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="7"/>
+    <col min="12" max="12" width="17.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.5" thickBot="1">
-      <c r="A2" s="13"/>
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
+      <c r="A2" s="9"/>
+      <c r="B2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="4" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="1">
         <v>2022</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13">
-      <c r="A4" s="13"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="1:14" ht="13.5">
+      <c r="A4" s="9"/>
+      <c r="B4" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="F4" s="11" t="s">
+      <c r="C4" s="2"/>
+      <c r="F4" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="7">
         <v>0.05</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="2">
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13">
-      <c r="A5" s="13"/>
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="1:14" ht="13.5">
+      <c r="A5" s="9"/>
+      <c r="B5" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="7">
         <v>1</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="2">
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13">
-      <c r="A6" s="13"/>
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="1:14" ht="13.5">
+      <c r="A6" s="9"/>
+      <c r="B6" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="7">
         <v>2025</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13">
-      <c r="A7" s="13"/>
-      <c r="B7" s="19" t="s">
+    <row r="7" spans="1:14" ht="13.5">
+      <c r="A7" s="9"/>
+      <c r="B7" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="7">
         <v>1</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13">
-      <c r="A8" s="13"/>
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="1:14" ht="13.5">
+      <c r="A8" s="9"/>
+      <c r="B8" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="7">
         <v>2.2201</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="2">
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13">
-      <c r="A9" s="13"/>
-      <c r="B9" s="19" t="s">
+    <row r="9" spans="1:14" ht="13.5">
+      <c r="A9" s="9"/>
+      <c r="B9" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="7">
         <v>2.1427</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="2">
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13">
-      <c r="A10" s="13"/>
-      <c r="B10" s="19" t="s">
+    <row r="10" spans="1:14" ht="13.5">
+      <c r="A10" s="9"/>
+      <c r="B10" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="7">
         <v>2.077</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="2">
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13">
-      <c r="A11" s="13"/>
-      <c r="B11" s="19" t="s">
+    <row r="11" spans="1:14" ht="13.5">
+      <c r="A11" s="9"/>
+      <c r="B11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="7">
         <v>2.0358000000000001</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="2">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13">
-      <c r="A12" s="13"/>
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="1:14" ht="13.5">
+      <c r="A12" s="9"/>
+      <c r="B12" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="7">
         <v>1.9870000000000001</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="2">
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="19" t="s">
+    <row r="13" spans="1:14" ht="13.5">
+      <c r="A13" s="9"/>
+      <c r="B13" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="7">
         <v>1.9192</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13">
-      <c r="A14" s="13"/>
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="1:14" ht="13.5">
+      <c r="A14" s="9"/>
+      <c r="B14" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="7">
         <v>1.8468</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="2">
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13">
-      <c r="A15" s="13"/>
-      <c r="B15" s="19" t="s">
+    <row r="15" spans="1:14" ht="13.5">
+      <c r="A15" s="9"/>
+      <c r="B15" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="7">
         <v>1.7799</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="2">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13">
-      <c r="A16" s="13"/>
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="1:14" ht="13.5">
+      <c r="A16" s="9"/>
+      <c r="B16" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="7">
         <v>1.722</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13">
-      <c r="A17" s="13"/>
-      <c r="B17" s="19" t="s">
+    <row r="17" spans="1:14" ht="13.5">
+      <c r="A17" s="9"/>
+      <c r="B17" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="7">
         <v>1.6836</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="2">
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13">
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:14" ht="13.5">
+      <c r="B18" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="7">
         <v>1.6446000000000001</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="2">
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13">
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="1:14" ht="13.5">
+      <c r="B19" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="7">
         <v>1.6102000000000001</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="2">
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13">
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="1:14" ht="13.5">
+      <c r="B20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="7">
         <v>1.5770999999999999</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="2">
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13">
-      <c r="B21" s="19" t="s">
+    <row r="21" spans="1:14" ht="13.5">
+      <c r="B21" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="7">
         <v>1.5488</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13">
-      <c r="B22" s="19" t="s">
+    <row r="22" spans="1:14" ht="13.5">
+      <c r="B22" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="7">
         <v>1.5224</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="2">
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13">
-      <c r="B23" s="19" t="s">
+    <row r="23" spans="1:14" ht="13.5">
+      <c r="B23" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="7">
         <v>1.5058</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="2">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13">
-      <c r="B24" s="19" t="s">
+    <row r="24" spans="1:14" ht="13.5">
+      <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="7">
         <v>1.4844999999999999</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="7">
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13">
-      <c r="B25" s="19" t="s">
+    <row r="25" spans="1:14" ht="13.5">
+      <c r="B25" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="7">
         <v>1.4518</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="7">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13">
-      <c r="B26" s="19" t="s">
+    <row r="26" spans="1:14" ht="13.5">
+      <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="7">
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13">
-      <c r="B27" s="19" t="s">
+    <row r="27" spans="1:14" ht="13.5">
+      <c r="B27" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="7">
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13">
-      <c r="B28" s="19" t="s">
+    <row r="28" spans="1:14" ht="13.5">
+      <c r="B28" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="7">
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13">
-      <c r="B29" s="19" t="s">
+    <row r="29" spans="1:14" ht="13.5">
+      <c r="B29" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="7">
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13">
-      <c r="B30" s="19" t="s">
+    <row r="30" spans="1:14" ht="13.5">
+      <c r="B30" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="7">
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13">
-      <c r="B31" s="19" t="s">
+    <row r="31" spans="1:14" ht="13.5">
+      <c r="B31" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="7">
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13">
-      <c r="B32" s="19" t="s">
+    <row r="32" spans="1:14" ht="13.5">
+      <c r="B32" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="7">
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13">
-      <c r="B33" s="19" t="s">
+    <row r="33" spans="2:9" ht="13.5">
+      <c r="B33" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="7">
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13">
-      <c r="B34" s="19" t="s">
+    <row r="34" spans="2:9" ht="13.5">
+      <c r="B34" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="7">
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13">
-      <c r="B35" s="19" t="s">
+    <row r="35" spans="2:9" ht="13.5">
+      <c r="B35" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="7">
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13">
-      <c r="B36" s="19" t="s">
+    <row r="36" spans="2:9" ht="13.5">
+      <c r="B36" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="7">
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13">
-      <c r="B37" s="19" t="s">
+    <row r="37" spans="2:9" ht="13.5">
+      <c r="B37" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="7">
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13">
-      <c r="B38" s="19" t="s">
+    <row r="38" spans="2:9" ht="13.5">
+      <c r="B38" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="7">
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13">
-      <c r="B39" s="19" t="s">
+    <row r="39" spans="2:9" ht="13.5">
+      <c r="B39" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="7">
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13">
-      <c r="B40" s="19" t="s">
+    <row r="40" spans="2:9" ht="13.5">
+      <c r="B40" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="7">
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13">
-      <c r="B41" s="19" t="s">
+    <row r="41" spans="2:9" ht="13.5">
+      <c r="B41" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="7">
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13">
-      <c r="B42" s="19" t="s">
+    <row r="42" spans="2:9" ht="13.5">
+      <c r="B42" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="7">
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13">
-      <c r="B43" s="19" t="s">
+    <row r="43" spans="2:9" ht="13.5">
+      <c r="B43" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="7">
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13">
-      <c r="B44" s="19" t="s">
+    <row r="44" spans="2:9" ht="13.5">
+      <c r="B44" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="7">
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13">
-      <c r="B45" s="19" t="s">
+    <row r="45" spans="2:9" ht="13.5">
+      <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13">
-      <c r="B46" s="19" t="s">
+    <row r="46" spans="2:9" ht="13.5">
+      <c r="B46" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="7">
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13">
-      <c r="B47" s="19" t="s">
+    <row r="47" spans="2:9" ht="13.5">
+      <c r="B47" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="7">
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13">
-      <c r="B48" s="19" t="s">
+    <row r="48" spans="2:9" ht="13.5">
+      <c r="B48" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="7">
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13">
-      <c r="B49" s="19" t="s">
+    <row r="49" spans="2:9" ht="13.5">
+      <c r="B49" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="7">
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13">
-      <c r="B50" s="19" t="s">
+    <row r="50" spans="2:9" ht="13.5">
+      <c r="B50" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="7">
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13">
-      <c r="B51" s="19" t="s">
+    <row r="51" spans="2:9" ht="13.5">
+      <c r="B51" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F51" s="11" t="str">
+      <c r="F51" s="7" t="str">
         <f>F46</f>
         <v>G_CUREX</v>
       </c>
-      <c r="G51" s="11" t="str">
+      <c r="G51" s="7" t="str">
         <f t="shared" ref="G51:I51" si="0">G46</f>
         <v>USD20</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="7">
         <f t="shared" si="0"/>
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13">
-      <c r="B52" s="19" t="s">
+    <row r="52" spans="2:9" ht="13.5">
+      <c r="B52" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13">
-      <c r="B53" s="19" t="s">
+    <row r="53" spans="2:9" ht="13.5">
+      <c r="B53" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13">
-      <c r="B54" s="19" t="s">
+    <row r="54" spans="2:9" ht="13.5">
+      <c r="B54" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="56" spans="2:9">
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9">
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="58" spans="2:9">
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="59" spans="2:9">
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="60" spans="2:9">
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="61" spans="2:9">
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="62" spans="2:9">
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="63" spans="2:9">
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="64" spans="2:9">
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="65" spans="6:9">
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="66" spans="6:9">
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="67" spans="6:9">
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="68" spans="6:9">
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="69" spans="6:9">
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="70" spans="6:9">
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="71" spans="6:9">
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I71" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="72" spans="6:9">
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I72" s="11">
+      <c r="I72" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="73" spans="6:9">
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="74" spans="6:9">
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I74" s="11">
+      <c r="I74" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="75" spans="6:9">
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="11">
+      <c r="I75" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="76" spans="6:9">
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I76" s="11">
+      <c r="I76" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="77" spans="6:9">
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I77" s="11">
+      <c r="I77" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="78" spans="6:9">
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I78" s="11">
+      <c r="I78" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="79" spans="6:9">
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="80" spans="6:9">
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="81" spans="6:9">
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="82" spans="6:9">
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="83" spans="6:9">
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="6:9">
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="85" spans="6:9">
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="86" spans="6:9">
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="87" spans="6:9">
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I87" s="11">
+      <c r="I87" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="88" spans="6:9">
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="89" spans="6:9">
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I89" s="11">
+      <c r="I89" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="90" spans="6:9">
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="91" spans="6:9">
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I91" s="11">
+      <c r="I91" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="6:9">
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="I92" s="11">
+      <c r="I92" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="93" spans="6:9">
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="94" spans="6:9">
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I94" s="11">
+      <c r="I94" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="95" spans="6:9">
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H95" s="11" t="str">
+      <c r="H95" s="7" t="str">
         <f>H51</f>
         <v>USD21_alt</v>
       </c>
-      <c r="I95" s="11">
+      <c r="I95" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.5" thickBot="1">
-      <c r="E99" s="20" t="s">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
+      <c r="E99" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
-      <c r="E100" s="4" t="s">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+      <c r="E100" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H100" s="4" t="s">
+      <c r="H100" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="1">
         <v>2022</v>
       </c>
-      <c r="J100" s="4" t="s">
+      <c r="J100" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.5">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
-      <c r="F101" s="21" t="s">
+      <c r="F101" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="G101" s="21" t="s">
+      <c r="G101" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H101" s="21" t="s">
+      <c r="H101" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I101" s="22">
+      <c r="I101" s="18">
         <f>1.10926234054354*I40</f>
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.5">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
-      <c r="F102" s="21" t="s">
+      <c r="F102" s="17" t="s">
         <v>191</v>
       </c>
       <c r="G102"/>
-      <c r="H102" s="21" t="s">
+      <c r="H102" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I102" s="22">
+      <c r="I102" s="18">
         <f>I84</f>
         <v>7.0000000000000007E-2</v>
       </c>
@@ -6743,273 +6944,273 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.81640625" style="6"/>
-    <col min="3" max="3" width="20.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.81640625" style="6"/>
+    <col min="1" max="2" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.5" thickBot="1">
-      <c r="B3" s="20" t="s">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
+      <c r="B3" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="2">
         <v>-1</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="12">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="12">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="12">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="12">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="13">
-      <c r="B23" s="18" t="s">
+    <row r="23" spans="2:4">
+      <c r="B23" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.5" thickBot="1">
-      <c r="B25" s="20" t="s">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
+      <c r="B25" s="16" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B26" s="4" t="s">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B26" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="2" t="s">
         <v>175</v>
       </c>
     </row>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1E127-73C2-4AAB-BC92-02A55278D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586CB307-842E-4BFF-97EE-F36A15F43438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="279">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -869,6 +869,12 @@
   </si>
   <si>
     <t>PDef1</t>
+  </si>
+  <si>
+    <t>elc_commercial</t>
+  </si>
+  <si>
+    <t>electricity used in commercial and public sector</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2355,7 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="431"/>
@@ -2371,11 +2377,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="234"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="234" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="438">
@@ -3306,1147 +3310,915 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:18" ht="18" thickBot="1">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="22" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="M3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="19"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="24" t="s">
+      <c r="M4" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="N4" s="24" t="s">
+      <c r="N4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="24" t="s">
+      <c r="P4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="24" t="s">
+      <c r="Q4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="R4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:18">
-      <c r="B5" s="19" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19" t="s">
+      <c r="M5" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" t="s">
         <v>214</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" t="s">
         <v>215</v>
       </c>
-      <c r="P5" s="19" t="s">
+      <c r="P5" t="s">
         <v>25</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="19" t="s">
+      <c r="R5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="19" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" t="s">
         <v>208</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19" t="s">
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19" t="s">
+      <c r="M6" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" t="s">
         <v>217</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" t="s">
         <v>218</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="P6" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="Q6" t="s">
         <v>35</v>
       </c>
-      <c r="R6" s="19" t="s">
+      <c r="R6" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:18">
-      <c r="B7" s="19" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19" t="s">
+      <c r="M7" t="s">
         <v>17</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" t="s">
         <v>219</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" t="s">
         <v>220</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="19" t="s">
+      <c r="Q7" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" s="19" t="s">
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19" t="s">
+      <c r="M8" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" t="s">
         <v>221</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" t="s">
         <v>222</v>
       </c>
-      <c r="P8" s="19" t="s">
+      <c r="P8" t="s">
         <v>25</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="Q8" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="19" t="s">
+      <c r="R8" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="19" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19" t="s">
+      <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19" t="s">
+      <c r="M9" t="s">
         <v>17</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="N9" t="s">
         <v>223</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" t="s">
         <v>224</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="P9" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" t="s">
         <v>35</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="R9" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="19" t="s">
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19" t="s">
+      <c r="E10" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19" t="s">
+      <c r="M10" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" t="s">
         <v>225</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" t="s">
         <v>226</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="Q10" t="s">
         <v>35</v>
       </c>
-      <c r="R10" s="19" t="s">
+      <c r="R10" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="19" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19" t="s">
+      <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19" t="s">
+      <c r="M11" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" t="s">
         <v>227</v>
       </c>
-      <c r="O11" s="19" t="s">
+      <c r="O11" t="s">
         <v>228</v>
       </c>
-      <c r="P11" s="19" t="s">
+      <c r="P11" t="s">
         <v>25</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="Q11" t="s">
         <v>35</v>
       </c>
-      <c r="R11" s="19" t="s">
+      <c r="R11" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="19" t="s">
+      <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19" t="s">
+      <c r="E12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19" t="s">
+      <c r="M12" t="s">
         <v>17</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" t="s">
         <v>229</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="O12" t="s">
         <v>230</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="P12" t="s">
         <v>25</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="Q12" t="s">
         <v>35</v>
       </c>
-      <c r="R12" s="19" t="s">
+      <c r="R12" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="19" t="s">
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19" t="s">
+      <c r="E13" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19" t="s">
+      <c r="M13" t="s">
         <v>17</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" t="s">
         <v>231</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" t="s">
         <v>232</v>
       </c>
-      <c r="P13" s="19" t="s">
+      <c r="P13" t="s">
         <v>25</v>
       </c>
-      <c r="Q13" s="19" t="s">
+      <c r="Q13" t="s">
         <v>35</v>
       </c>
-      <c r="R13" s="19" t="s">
+      <c r="R13" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="19" t="s">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" t="s">
         <v>204</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" t="s">
         <v>206</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19" t="s">
+      <c r="M14" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" t="s">
         <v>233</v>
       </c>
-      <c r="O14" s="19" t="s">
+      <c r="O14" t="s">
         <v>234</v>
       </c>
-      <c r="P14" s="19" t="s">
+      <c r="P14" t="s">
         <v>25</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="Q14" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="19" t="s">
+      <c r="R14" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="19" t="s">
+      <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19" t="s">
+      <c r="M15" t="s">
         <v>17</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" t="s">
         <v>235</v>
       </c>
-      <c r="O15" s="19" t="s">
+      <c r="O15" t="s">
         <v>236</v>
       </c>
-      <c r="P15" s="19" t="s">
+      <c r="P15" t="s">
         <v>25</v>
       </c>
-      <c r="Q15" s="19" t="s">
+      <c r="Q15" t="s">
         <v>35</v>
       </c>
-      <c r="R15" s="19" t="s">
+      <c r="R15" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="19" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19" t="s">
+      <c r="I16" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19" t="s">
+      <c r="M16" t="s">
         <v>17</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" t="s">
         <v>237</v>
       </c>
-      <c r="O16" s="19" t="s">
+      <c r="O16" t="s">
         <v>238</v>
       </c>
-      <c r="P16" s="19" t="s">
+      <c r="P16" t="s">
         <v>25</v>
       </c>
-      <c r="Q16" s="19" t="s">
+      <c r="Q16" t="s">
         <v>35</v>
       </c>
-      <c r="R16" s="19" t="s">
+      <c r="R16" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="19" t="s">
+      <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" t="s">
         <v>203</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19" t="s">
+      <c r="M17" t="s">
         <v>17</v>
       </c>
-      <c r="N17" s="19" t="s">
+      <c r="N17" t="s">
         <v>239</v>
       </c>
-      <c r="O17" s="19" t="s">
+      <c r="O17" t="s">
         <v>240</v>
       </c>
-      <c r="P17" s="19" t="s">
+      <c r="P17" t="s">
         <v>25</v>
       </c>
-      <c r="Q17" s="19" t="s">
+      <c r="Q17" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="19" t="s">
+      <c r="R17" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="19" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19" t="s">
+      <c r="M18" t="s">
         <v>17</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" t="s">
         <v>241</v>
       </c>
-      <c r="O18" s="19" t="s">
+      <c r="O18" t="s">
         <v>242</v>
       </c>
-      <c r="P18" s="19" t="s">
+      <c r="P18" t="s">
         <v>25</v>
       </c>
-      <c r="Q18" s="19" t="s">
+      <c r="Q18" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="19" t="s">
+      <c r="R18" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:18">
-      <c r="B19" s="19" t="s">
+      <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19" t="s">
+      <c r="M19" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="19" t="s">
+      <c r="N19" t="s">
         <v>243</v>
       </c>
-      <c r="O19" s="19" t="s">
+      <c r="O19" t="s">
         <v>244</v>
       </c>
-      <c r="P19" s="19" t="s">
+      <c r="P19" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" s="19" t="s">
+      <c r="Q19" t="s">
         <v>35</v>
       </c>
-      <c r="R19" s="19" t="s">
+      <c r="R19" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="20" spans="2:18">
-      <c r="B20" s="19" t="s">
+      <c r="B20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" t="s">
+        <v>278</v>
+      </c>
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19" t="s">
+      <c r="M21" t="s">
         <v>17</v>
       </c>
-      <c r="N20" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="O20" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="P20" s="19" t="s">
+      <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
         <v>25</v>
       </c>
-      <c r="Q20" s="19" t="s">
+      <c r="Q21" t="s">
         <v>35</v>
       </c>
-      <c r="R20" s="19" t="s">
+      <c r="R21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="2:18">
-      <c r="B21" s="19" t="s">
+    <row r="22" spans="2:18">
+      <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C22" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D22" t="s">
         <v>197</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E22" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F22" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19" t="s">
+      <c r="M22" t="s">
         <v>17</v>
       </c>
-      <c r="N21" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="P21" s="19" t="s">
+      <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
         <v>25</v>
       </c>
-      <c r="Q21" s="19" t="s">
+      <c r="Q22" t="s">
         <v>35</v>
       </c>
-      <c r="R21" s="19" t="s">
+      <c r="R22" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="22" spans="2:18">
-      <c r="B22" s="19" t="s">
+    <row r="23" spans="2:18">
+      <c r="B23" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C23" t="s">
         <v>193</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D23" t="s">
         <v>194</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E23" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19" t="s">
+      <c r="M23" t="s">
         <v>17</v>
       </c>
-      <c r="N22" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="P22" s="19" t="s">
+      <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" t="s">
         <v>25</v>
       </c>
-      <c r="Q22" s="19" t="s">
+      <c r="Q23" t="s">
         <v>35</v>
       </c>
-      <c r="R22" s="19" t="s">
+      <c r="R23" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="2:18">
-      <c r="B23" s="19" t="s">
+    <row r="24" spans="2:18">
+      <c r="B24" t="s">
         <v>192</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C24" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19" t="s">
+      <c r="E24" t="s">
         <v>195</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19" t="s">
+      <c r="M24" t="s">
         <v>17</v>
       </c>
-      <c r="N23" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="O23" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="P23" s="19" t="s">
+      <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" t="s">
         <v>25</v>
       </c>
-      <c r="Q23" s="19" t="s">
+      <c r="Q24" t="s">
         <v>35</v>
       </c>
-      <c r="R23" s="19" t="s">
+      <c r="R24" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="2:18">
-      <c r="B24" s="19" t="s">
+    <row r="25" spans="2:18">
+      <c r="B25" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C25" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19" t="s">
+      <c r="E25" t="s">
         <v>195</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19" t="s">
+      <c r="M25" t="s">
         <v>17</v>
       </c>
-      <c r="N24" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="O24" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="P24" s="19" t="s">
+      <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
+        <v>256</v>
+      </c>
+      <c r="P25" t="s">
         <v>25</v>
       </c>
-      <c r="Q24" s="19" t="s">
+      <c r="Q25" t="s">
         <v>35</v>
       </c>
-      <c r="R24" s="19" t="s">
+      <c r="R25" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="25" spans="2:18">
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19" t="s">
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="P25" s="19" t="s">
+      <c r="N26" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" t="s">
         <v>25</v>
       </c>
-      <c r="Q25" s="19" t="s">
+      <c r="Q26" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="19" t="s">
+      <c r="R26" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="26" spans="2:18">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19" t="s">
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
         <v>17</v>
       </c>
-      <c r="N26" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="O26" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="P26" s="19" t="s">
+      <c r="N27" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s">
+        <v>260</v>
+      </c>
+      <c r="P27" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="19" t="s">
+      <c r="Q27" t="s">
         <v>35</v>
       </c>
-      <c r="R26" s="19" t="s">
+      <c r="R27" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="27" spans="2:18">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19" t="s">
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
         <v>17</v>
       </c>
-      <c r="N27" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="P27" s="19" t="s">
+      <c r="N28" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" t="s">
+        <v>262</v>
+      </c>
+      <c r="P28" t="s">
         <v>25</v>
       </c>
-      <c r="Q27" s="19" t="s">
+      <c r="Q28" t="s">
         <v>35</v>
       </c>
-      <c r="R27" s="19" t="s">
+      <c r="R28" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="2:18">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19" t="s">
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
         <v>17</v>
       </c>
-      <c r="N28" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="O28" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="P28" s="19" t="s">
+      <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
+        <v>264</v>
+      </c>
+      <c r="P29" t="s">
         <v>25</v>
       </c>
-      <c r="Q28" s="19" t="s">
+      <c r="Q29" t="s">
         <v>35</v>
       </c>
-      <c r="R28" s="19" t="s">
+      <c r="R29" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="2:18">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19" t="s">
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
         <v>17</v>
       </c>
-      <c r="N29" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="P29" s="19" t="s">
+      <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
+        <v>266</v>
+      </c>
+      <c r="P30" t="s">
         <v>25</v>
       </c>
-      <c r="Q29" s="19" t="s">
+      <c r="Q30" t="s">
         <v>35</v>
       </c>
-      <c r="R29" s="19" t="s">
+      <c r="R30" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="30" spans="2:18">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19" t="s">
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
         <v>17</v>
       </c>
-      <c r="N30" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="O30" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="P30" s="19" t="s">
+      <c r="N31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s">
+        <v>268</v>
+      </c>
+      <c r="P31" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="19" t="s">
+      <c r="Q31" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="19" t="s">
+      <c r="R31" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="2:18">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19" t="s">
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
         <v>17</v>
       </c>
-      <c r="N31" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="O31" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="P31" s="19" t="s">
+      <c r="N32" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s">
+        <v>270</v>
+      </c>
+      <c r="P32" t="s">
         <v>25</v>
       </c>
-      <c r="Q31" s="19" t="s">
+      <c r="Q32" t="s">
         <v>35</v>
       </c>
-      <c r="R31" s="19" t="s">
+      <c r="R32" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="32" spans="2:18">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19" t="s">
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
         <v>17</v>
       </c>
-      <c r="N32" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="O32" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="P32" s="19" t="s">
+      <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" t="s">
         <v>25</v>
       </c>
-      <c r="Q32" s="19" t="s">
+      <c r="Q33" t="s">
         <v>35</v>
       </c>
-      <c r="R32" s="19" t="s">
+      <c r="R33" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="13:18">
-      <c r="M33" s="19" t="s">
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
         <v>17</v>
       </c>
-      <c r="N33" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="O33" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="P33" s="19" t="s">
+      <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" t="s">
         <v>25</v>
       </c>
-      <c r="Q33" s="19" t="s">
+      <c r="Q34" t="s">
         <v>35</v>
       </c>
-      <c r="R33" s="19" t="s">
+      <c r="R34" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="34" spans="13:18">
-      <c r="M34" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="N34" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="O34" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C12:C338">
-    <sortCondition ref="C23:C338"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C12:C339">
+    <sortCondition ref="C24:C339"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586CB307-842E-4BFF-97EE-F36A15F43438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621948D0-ADC5-4658-A15F-C4300F589B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -865,9 +865,6 @@
     <t>onshore wind electricity generation in cluster -- 10</t>
   </si>
   <si>
-    <t>msy7_2050</t>
-  </si>
-  <si>
     <t>PDef1</t>
   </si>
   <si>
@@ -875,6 +872,9 @@
   </si>
   <si>
     <t>electricity used in commercial and public sector</t>
+  </si>
+  <si>
+    <t>msy6_2050</t>
   </si>
 </sst>
 </file>
@@ -3852,10 +3852,10 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" t="s">
         <v>277</v>
-      </c>
-      <c r="D20" t="s">
-        <v>278</v>
       </c>
       <c r="M20" t="s">
         <v>17</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="2">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -4255,7 +4255,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -4268,22 +4268,22 @@
     </row>
     <row r="12" spans="2:7" ht="15">
       <c r="B12" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="4" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
-        <v>msy7_2050</v>
+        <v>msy7_2053</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
+        <f>"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
         <v>msy6_2050</v>
       </c>
       <c r="G12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>msy5_2050</v>
+        <f t="shared" ref="G12" si="0">"msy"&amp;COUNT(G14:G45)&amp;"_"&amp;MAX(G14:G45)</f>
+        <v>msy5_2053</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15">
@@ -4302,16 +4302,15 @@
         <v>46</v>
       </c>
       <c r="E14" s="2">
-        <f t="shared" ref="E14:G14" si="1">$B$4</f>
-        <v>2022</v>
+        <f>$B$4</f>
+        <v>2025</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="1"/>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="1"/>
-        <v>2022</v>
+        <f t="shared" ref="G14" si="1">$B$4</f>
+        <v>2025</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="15">
@@ -4323,15 +4322,14 @@
       </c>
       <c r="E15" s="2">
         <f>E14+3</f>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F15" s="2">
-        <f>F14+3</f>
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="G15" s="2">
         <f>G14+3</f>
-        <v>2025</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="15">
@@ -4343,15 +4341,14 @@
       </c>
       <c r="E16" s="2">
         <f>E15+5</f>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="F16" s="2">
-        <f>F15+5</f>
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="G16" s="2">
         <f>G15+5</f>
-        <v>2030</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15">
@@ -4363,15 +4360,14 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="F17" s="2">
-        <f>F16+5</f>
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="G17" s="2">
         <f>G16+10</f>
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="15">
@@ -4383,15 +4379,14 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" si="2"/>
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="F18" s="2">
-        <f>F17+5</f>
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" ref="G18" si="3">G17+10</f>
-        <v>2050</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15">
@@ -4403,10 +4398,9 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" si="2"/>
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="F19" s="2">
-        <f>F18+10</f>
         <v>2050</v>
       </c>
     </row>
@@ -4417,7 +4411,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" si="2"/>
-        <v>2050</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15">

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621948D0-ADC5-4658-A15F-C4300F589B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FD8CA6-08AD-4827-A447-86D71D77B8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -874,7 +874,7 @@
     <t>electricity used in commercial and public sector</t>
   </si>
   <si>
-    <t>msy6_2050</t>
+    <t>msy7_2050</t>
   </si>
 </sst>
 </file>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E12" s="4" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
-        <v>msy7_2053</v>
+        <v>msy7_2050</v>
       </c>
       <c r="F12" s="4" t="str">
         <f>"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G12" s="4" t="str">
         <f t="shared" ref="G12" si="0">"msy"&amp;COUNT(G14:G45)&amp;"_"&amp;MAX(G14:G45)</f>
-        <v>msy5_2053</v>
+        <v>msy5_2050</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="E14" s="2">
         <f>$B$4</f>
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F14" s="2">
         <v>2025</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" ref="G14" si="1">$B$4</f>
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="15">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="E15" s="2">
         <f>E14+3</f>
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="F15" s="2">
         <v>2030</v>
       </c>
       <c r="G15" s="2">
         <f>G14+3</f>
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="15">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="E16" s="2">
         <f>E15+5</f>
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="F16" s="2">
         <v>2035</v>
       </c>
       <c r="G16" s="2">
         <f>G15+5</f>
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15">
@@ -4360,14 +4360,14 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="F17" s="2">
         <v>2040</v>
       </c>
       <c r="G17" s="2">
         <f>G16+10</f>
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="15">
@@ -4379,14 +4379,14 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" si="2"/>
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="F18" s="2">
         <v>2045</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" ref="G18" si="3">G17+10</f>
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" si="2"/>
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="F19" s="2">
         <v>2050</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" si="2"/>
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15">

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FD8CA6-08AD-4827-A447-86D71D77B8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A338A-4A0E-4102-A22D-C3DD5E06221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="279">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1279,6 +1279,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="47">
@@ -3311,7 +3313,7 @@
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
@@ -3856,6 +3858,9 @@
       </c>
       <c r="D20" t="s">
         <v>277</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
       </c>
       <c r="M20" t="s">
         <v>17</v>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A338A-4A0E-4102-A22D-C3DD5E06221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2974C9-9781-4AAA-9F5C-D7612F249764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
     <sheet name="fuels" sheetId="2" r:id="rId2"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId3"/>
-    <sheet name="System Settings" sheetId="4" r:id="rId4"/>
-    <sheet name="Constants" sheetId="5" r:id="rId5"/>
-    <sheet name="reporting options" sheetId="6" r:id="rId6"/>
+    <sheet name="grids" sheetId="7" r:id="rId3"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId4"/>
+    <sheet name="System Settings" sheetId="4" r:id="rId5"/>
+    <sheet name="Constants" sheetId="5" r:id="rId6"/>
+    <sheet name="reporting options" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="311">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -875,6 +876,102 @@
   </si>
   <si>
     <t>msy7_2050</t>
+  </si>
+  <si>
+    <t>e_harku_330</t>
+  </si>
+  <si>
+    <t>Harku alajaam</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>e_pussi_330</t>
+  </si>
+  <si>
+    <t>Pussi alajaam</t>
+  </si>
+  <si>
+    <t>e_kilingi_nomme_330</t>
+  </si>
+  <si>
+    <t>Killingi-Nomme alajaam</t>
+  </si>
+  <si>
+    <t>e_tsirguliina_330</t>
+  </si>
+  <si>
+    <t>Tsirguliina alajaam</t>
+  </si>
+  <si>
+    <t>e_tartu_330</t>
+  </si>
+  <si>
+    <t>Tartu alajaam</t>
+  </si>
+  <si>
+    <t>e_arukula_330</t>
+  </si>
+  <si>
+    <t>Arukula alajaam</t>
+  </si>
+  <si>
+    <t>e_baltiej_330</t>
+  </si>
+  <si>
+    <t>Balti EJ alajaam</t>
+  </si>
+  <si>
+    <t>e_viru_330</t>
+  </si>
+  <si>
+    <t>Viru alajaam</t>
+  </si>
+  <si>
+    <t>e_kiisa_330</t>
+  </si>
+  <si>
+    <t>Kiisa alajaam</t>
+  </si>
+  <si>
+    <t>e_paide_330</t>
+  </si>
+  <si>
+    <t>Paide alajaam</t>
+  </si>
+  <si>
+    <t>e_sopi_330</t>
+  </si>
+  <si>
+    <t>Sopi alajaam</t>
+  </si>
+  <si>
+    <t>e_sindi_330</t>
+  </si>
+  <si>
+    <t>Sindi alajaam</t>
+  </si>
+  <si>
+    <t>e_mustvee_330</t>
+  </si>
+  <si>
+    <t>Mustvee alajaam</t>
+  </si>
+  <si>
+    <t>e_rakvere_330</t>
+  </si>
+  <si>
+    <t>Rakvere alajaam</t>
+  </si>
+  <si>
+    <t>e_lihula_330</t>
+  </si>
+  <si>
+    <t>Lihula alajaam</t>
+  </si>
+  <si>
+    <t>~fi_comm</t>
   </si>
 </sst>
 </file>
@@ -4230,6 +4327,393 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CD4434-6BD0-409F-A92E-16A0D49E7A83}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
@@ -4491,7 +4975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
@@ -5072,7 +5556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
@@ -6712,7 +7196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2974C9-9781-4AAA-9F5C-D7612F249764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37A9B8C-4C6C-4C85-BBDB-C1BB6D7F38D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -683,27 +683,9 @@
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 1</t>
-  </si>
-  <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 2</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 3</t>
-  </si>
-  <si>
     <t>elc_spv_004</t>
   </si>
   <si>
@@ -728,24 +710,12 @@
     <t>solar electricity generation in cluster -- 7</t>
   </si>
   <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 8</t>
-  </si>
-  <si>
     <t>elc_spv_009</t>
   </si>
   <si>
     <t>solar electricity generation in cluster -- 9</t>
   </si>
   <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 10</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
@@ -972,6 +942,36 @@
   </si>
   <si>
     <t>~fi_comm</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Harju</t>
+  </si>
+  <si>
+    <t>elc_spv_harju</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Parnu</t>
+  </si>
+  <si>
+    <t>elc_spv_parnu</t>
+  </si>
+  <si>
+    <t>elc_spv_laane_viru</t>
+  </si>
+  <si>
+    <t>elc_spv_tartu</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Tartu</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Laane-Viru</t>
+  </si>
+  <si>
+    <t>elc_spv_viljandi</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster Viljandi</t>
   </si>
 </sst>
 </file>
@@ -3405,7 +3405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R34"/>
+  <dimension ref="B3:R44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -3416,7 +3416,7 @@
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="45.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
@@ -3498,10 +3498,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3510,7 +3510,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3527,10 +3527,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>306</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3539,7 +3539,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3556,10 +3556,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>305</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3568,7 +3568,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3585,10 +3585,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3597,7 +3597,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -3614,10 +3614,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>309</v>
       </c>
       <c r="O9" t="s">
-        <v>224</v>
+        <v>310</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3626,7 +3626,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -3655,7 +3655,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -3684,7 +3684,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -3713,7 +3713,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -3742,7 +3742,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -3774,7 +3774,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -3806,7 +3806,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -3847,7 +3847,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -3879,7 +3879,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -3911,7 +3911,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -3943,7 +3943,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -3951,10 +3951,10 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3975,7 +3975,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4007,7 +4007,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4045,7 +4045,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4077,7 +4077,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4106,7 +4106,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4135,7 +4135,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4155,7 +4155,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -4175,7 +4175,7 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -4195,7 +4195,7 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -4215,107 +4215,107 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>215</v>
+      </c>
+      <c r="O40" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="M30" t="s">
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
         <v>17</v>
       </c>
-      <c r="N30" t="s">
-        <v>265</v>
-      </c>
-      <c r="O30" t="s">
-        <v>266</v>
-      </c>
-      <c r="P30" t="s">
+      <c r="N41" t="s">
+        <v>217</v>
+      </c>
+      <c r="O41" t="s">
+        <v>218</v>
+      </c>
+      <c r="P41" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="Q41" t="s">
         <v>35</v>
       </c>
-      <c r="R30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18">
-      <c r="M31" t="s">
+      <c r="R41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
         <v>17</v>
       </c>
-      <c r="N31" t="s">
-        <v>267</v>
-      </c>
-      <c r="O31" t="s">
-        <v>268</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="N42" t="s">
+        <v>219</v>
+      </c>
+      <c r="O42" t="s">
+        <v>220</v>
+      </c>
+      <c r="P42" t="s">
         <v>25</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="Q42" t="s">
         <v>35</v>
       </c>
-      <c r="R31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18">
-      <c r="M32" t="s">
+      <c r="R42" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
         <v>17</v>
       </c>
-      <c r="N32" t="s">
-        <v>269</v>
-      </c>
-      <c r="O32" t="s">
-        <v>270</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="N43" t="s">
+        <v>221</v>
+      </c>
+      <c r="O43" t="s">
+        <v>222</v>
+      </c>
+      <c r="P43" t="s">
         <v>25</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="Q43" t="s">
         <v>35</v>
       </c>
-      <c r="R32" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="13:18">
-      <c r="M33" t="s">
+      <c r="R43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
         <v>17</v>
       </c>
-      <c r="N33" t="s">
-        <v>271</v>
-      </c>
-      <c r="O33" t="s">
-        <v>272</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="N44" t="s">
+        <v>223</v>
+      </c>
+      <c r="O44" t="s">
+        <v>224</v>
+      </c>
+      <c r="P44" t="s">
         <v>25</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Q44" t="s">
         <v>35</v>
       </c>
-      <c r="R33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="13:18">
-      <c r="M34" t="s">
-        <v>17</v>
-      </c>
-      <c r="N34" t="s">
-        <v>273</v>
-      </c>
-      <c r="O34" t="s">
-        <v>274</v>
-      </c>
-      <c r="P34" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" t="s">
-        <v>216</v>
+      <c r="R44" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4337,7 +4337,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4368,10 +4368,10 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -4380,10 +4380,10 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4391,10 +4391,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -4403,10 +4403,10 @@
         <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4414,10 +4414,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -4426,10 +4426,10 @@
         <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4437,10 +4437,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -4449,10 +4449,10 @@
         <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4460,10 +4460,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -4472,10 +4472,10 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4483,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -4495,10 +4495,10 @@
         <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4506,10 +4506,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -4518,10 +4518,10 @@
         <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4529,10 +4529,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -4541,10 +4541,10 @@
         <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4552,10 +4552,10 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -4564,10 +4564,10 @@
         <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4575,10 +4575,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -4587,10 +4587,10 @@
         <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4598,10 +4598,10 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -4610,10 +4610,10 @@
         <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4621,10 +4621,10 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C14" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
@@ -4633,10 +4633,10 @@
         <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4644,10 +4644,10 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -4656,10 +4656,10 @@
         <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4667,10 +4667,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
@@ -4679,10 +4679,10 @@
         <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4690,10 +4690,10 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -4702,10 +4702,10 @@
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4744,7 +4744,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="2" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -4757,7 +4757,7 @@
     </row>
     <row r="12" spans="2:7" ht="15">
       <c r="B12" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37A9B8C-4C6C-4C85-BBDB-C1BB6D7F38D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF3DCCF-7DE9-48F6-9043-3B892946F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
     <sheet name="fuels" sheetId="2" r:id="rId2"/>
-    <sheet name="grids" sheetId="7" r:id="rId3"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId4"/>
-    <sheet name="System Settings" sheetId="4" r:id="rId5"/>
-    <sheet name="Constants" sheetId="5" r:id="rId6"/>
-    <sheet name="reporting options" sheetId="6" r:id="rId7"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId3"/>
+    <sheet name="System Settings" sheetId="4" r:id="rId4"/>
+    <sheet name="Constants" sheetId="5" r:id="rId5"/>
+    <sheet name="reporting options" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="279">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -846,102 +845,6 @@
   </si>
   <si>
     <t>msy7_2050</t>
-  </si>
-  <si>
-    <t>e_harku_330</t>
-  </si>
-  <si>
-    <t>Harku alajaam</t>
-  </si>
-  <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>e_pussi_330</t>
-  </si>
-  <si>
-    <t>Pussi alajaam</t>
-  </si>
-  <si>
-    <t>e_kilingi_nomme_330</t>
-  </si>
-  <si>
-    <t>Killingi-Nomme alajaam</t>
-  </si>
-  <si>
-    <t>e_tsirguliina_330</t>
-  </si>
-  <si>
-    <t>Tsirguliina alajaam</t>
-  </si>
-  <si>
-    <t>e_tartu_330</t>
-  </si>
-  <si>
-    <t>Tartu alajaam</t>
-  </si>
-  <si>
-    <t>e_arukula_330</t>
-  </si>
-  <si>
-    <t>Arukula alajaam</t>
-  </si>
-  <si>
-    <t>e_baltiej_330</t>
-  </si>
-  <si>
-    <t>Balti EJ alajaam</t>
-  </si>
-  <si>
-    <t>e_viru_330</t>
-  </si>
-  <si>
-    <t>Viru alajaam</t>
-  </si>
-  <si>
-    <t>e_kiisa_330</t>
-  </si>
-  <si>
-    <t>Kiisa alajaam</t>
-  </si>
-  <si>
-    <t>e_paide_330</t>
-  </si>
-  <si>
-    <t>Paide alajaam</t>
-  </si>
-  <si>
-    <t>e_sopi_330</t>
-  </si>
-  <si>
-    <t>Sopi alajaam</t>
-  </si>
-  <si>
-    <t>e_sindi_330</t>
-  </si>
-  <si>
-    <t>Sindi alajaam</t>
-  </si>
-  <si>
-    <t>e_mustvee_330</t>
-  </si>
-  <si>
-    <t>Mustvee alajaam</t>
-  </si>
-  <si>
-    <t>e_rakvere_330</t>
-  </si>
-  <si>
-    <t>Rakvere alajaam</t>
-  </si>
-  <si>
-    <t>e_lihula_330</t>
-  </si>
-  <si>
-    <t>Lihula alajaam</t>
-  </si>
-  <si>
-    <t>~fi_comm</t>
   </si>
   <si>
     <t>solar electricity generation in Harju</t>
@@ -3331,15 +3234,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3406,22 +3309,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.7265625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="18" thickBot="1">
+    <row r="3" spans="2:18" ht="17.5" thickBot="1">
       <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
@@ -3440,7 +3343,7 @@
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
@@ -3498,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="O5" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3527,10 +3430,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="O6" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3556,10 +3459,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="O7" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3585,10 +3488,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="O8" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3614,10 +3517,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="O9" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -4327,404 +4230,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CD4434-6BD0-409F-A92E-16A0D49E7A83}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>271</v>
-      </c>
-      <c r="G4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>271</v>
-      </c>
-      <c r="G7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>271</v>
-      </c>
-      <c r="G9" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" t="s">
-        <v>285</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" t="s">
-        <v>271</v>
-      </c>
-      <c r="G10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>286</v>
-      </c>
-      <c r="C11" t="s">
-        <v>287</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" t="s">
-        <v>271</v>
-      </c>
-      <c r="G11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>288</v>
-      </c>
-      <c r="C12" t="s">
-        <v>289</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>271</v>
-      </c>
-      <c r="G12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>290</v>
-      </c>
-      <c r="C13" t="s">
-        <v>291</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>271</v>
-      </c>
-      <c r="G13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C14" t="s">
-        <v>293</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" t="s">
-        <v>271</v>
-      </c>
-      <c r="G14" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>294</v>
-      </c>
-      <c r="C15" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" t="s">
-        <v>271</v>
-      </c>
-      <c r="G15" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>296</v>
-      </c>
-      <c r="C16" t="s">
-        <v>297</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" t="s">
-        <v>271</v>
-      </c>
-      <c r="G16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" t="s">
-        <v>271</v>
-      </c>
-      <c r="G17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="14.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="9.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="2"/>
+    <col min="4" max="4" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4755,7 +4271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15">
+    <row r="12" spans="2:7" ht="14.5">
       <c r="B12" s="3" t="s">
         <v>265</v>
       </c>
@@ -4775,7 +4291,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15">
+    <row r="13" spans="2:7" ht="14.5">
       <c r="B13" s="5">
         <v>1</v>
       </c>
@@ -4783,7 +4299,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15">
+    <row r="14" spans="2:7" ht="14.5">
       <c r="B14" s="5">
         <v>5</v>
       </c>
@@ -4802,7 +4318,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15">
+    <row r="15" spans="2:7" ht="14.5">
       <c r="B15" s="5">
         <v>5</v>
       </c>
@@ -4821,7 +4337,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15">
+    <row r="16" spans="2:7" ht="14.5">
       <c r="B16" s="5">
         <v>5</v>
       </c>
@@ -4840,7 +4356,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15">
+    <row r="17" spans="2:7" ht="14.5">
       <c r="B17" s="5">
         <v>5</v>
       </c>
@@ -4859,7 +4375,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15">
+    <row r="18" spans="2:7" ht="14.5">
       <c r="B18" s="5">
         <v>5</v>
       </c>
@@ -4878,7 +4394,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15">
+    <row r="19" spans="2:7" ht="14.5">
       <c r="B19" s="5">
         <v>5</v>
       </c>
@@ -4893,7 +4409,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15">
+    <row r="20" spans="2:7" ht="14.5">
       <c r="B20" s="5"/>
       <c r="D20" s="2" t="s">
         <v>46</v>
@@ -4903,70 +4419,70 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15">
+    <row r="21" spans="2:7" ht="14.5">
       <c r="B21" s="5"/>
       <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15">
+    <row r="22" spans="2:7" ht="14.5">
       <c r="B22" s="5"/>
       <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15">
+    <row r="23" spans="2:7" ht="14.5">
       <c r="B23" s="5"/>
       <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15">
+    <row r="24" spans="2:7" ht="14.5">
       <c r="B24" s="5"/>
       <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15">
+    <row r="25" spans="2:7" ht="14.5">
       <c r="B25" s="5"/>
       <c r="D25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15">
+    <row r="26" spans="2:7" ht="14.5">
       <c r="B26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15">
+    <row r="27" spans="2:7" ht="14.5">
       <c r="B27" s="5"/>
       <c r="D27" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15">
+    <row r="28" spans="2:7" ht="14.5">
       <c r="B28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="15">
+    <row r="29" spans="2:7" ht="14.5">
       <c r="B29" s="5"/>
       <c r="D29" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="15">
+    <row r="30" spans="2:7" ht="14.5">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="2:7" ht="15">
+    <row r="31" spans="2:7" ht="14.5">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="2:7" ht="15">
+    <row r="32" spans="2:7" ht="14.5">
       <c r="B32" s="5"/>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" spans="2:2" ht="14.5">
       <c r="B33" s="5"/>
     </row>
   </sheetData>
@@ -4975,31 +4491,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
-    <col min="2" max="2" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7"/>
+    <col min="2" max="2" width="8.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="7"/>
+    <col min="9" max="9" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.453125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
+    <row r="1" spans="2:12" ht="12.5">
       <c r="B1" s="2"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="2:12" ht="12.75">
+    <row r="2" spans="2:12" ht="12.5">
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -5010,7 +4526,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="2:12" ht="12.75">
+    <row r="3" spans="2:12" ht="12.5">
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
@@ -5029,7 +4545,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" ht="12">
       <c r="B5" s="11" t="s">
         <v>48</v>
       </c>
@@ -5138,7 +4654,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" ht="12">
       <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
@@ -5186,7 +4702,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.75">
+    <row r="18" spans="2:14" ht="12.5">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -5197,7 +4713,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="2:14" ht="12.75">
+    <row r="19" spans="2:14" ht="12.5">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -5208,7 +4724,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="2:14" ht="12.75">
+    <row r="20" spans="2:14" ht="12.5">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -5219,7 +4735,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
+    <row r="21" spans="2:14" ht="14.5">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -5234,7 +4750,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="15">
+    <row r="22" spans="2:14" ht="14.5">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -5249,7 +4765,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="15">
+    <row r="23" spans="2:14" ht="14.5">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -5264,7 +4780,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="15">
+    <row r="24" spans="2:14" ht="14.5">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -5279,7 +4795,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="15">
+    <row r="25" spans="2:14" ht="14.5">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -5294,7 +4810,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="15">
+    <row r="26" spans="2:14" ht="14.5">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -5309,7 +4825,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="15">
+    <row r="27" spans="2:14" ht="14.5">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -5324,7 +4840,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="15">
+    <row r="28" spans="2:14" ht="14.5">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -5339,7 +4855,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="15">
+    <row r="29" spans="2:14" ht="14.5">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -5354,7 +4870,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="15">
+    <row r="30" spans="2:14" ht="14.5">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -5369,7 +4885,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="15">
+    <row r="31" spans="2:14" ht="14.5">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -5384,7 +4900,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="15">
+    <row r="32" spans="2:14" ht="14.5">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -5399,7 +4915,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="15">
+    <row r="33" spans="2:14" ht="14.5">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -5414,7 +4930,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="15">
+    <row r="34" spans="2:14" ht="14.5">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -5429,7 +4945,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="15">
+    <row r="35" spans="2:14" ht="14.5">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -5444,7 +4960,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="15">
+    <row r="36" spans="2:14" ht="14.5">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -5459,7 +4975,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="15">
+    <row r="37" spans="2:14" ht="14.5">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -5474,7 +4990,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="15">
+    <row r="38" spans="2:14" ht="14.5">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -5489,7 +5005,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="15">
+    <row r="39" spans="2:14" ht="14.5">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -5504,7 +5020,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="15">
+    <row r="40" spans="2:14" ht="14.5">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5519,7 +5035,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="15">
+    <row r="41" spans="2:14" ht="14.5">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5534,7 +5050,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="15">
+    <row r="42" spans="2:14" ht="14.5">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5556,28 +5072,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
-    <col min="2" max="2" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="7"/>
-    <col min="5" max="5" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7"/>
+    <col min="2" max="2" width="12.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" style="7"/>
+    <col min="5" max="5" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="7"/>
-    <col min="12" max="12" width="17.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="7"/>
+    <col min="10" max="10" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" style="7"/>
+    <col min="12" max="12" width="17.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.453125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="18" thickBot="1">
+    <row r="2" spans="1:14" ht="17.5" thickBot="1">
       <c r="A2" s="9"/>
       <c r="B2" s="16" t="s">
         <v>68</v>
@@ -5591,7 +5107,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="1" t="s">
         <v>70</v>
@@ -5624,7 +5140,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13">
       <c r="A4" s="9"/>
       <c r="B4" s="15" t="s">
         <v>134</v>
@@ -5649,7 +5165,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13">
       <c r="A5" s="9"/>
       <c r="B5" s="15" t="s">
         <v>72</v>
@@ -5676,7 +5192,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13">
       <c r="A6" s="9"/>
       <c r="B6" s="15" t="s">
         <v>73</v>
@@ -5697,7 +5213,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13">
       <c r="A7" s="9"/>
       <c r="B7" s="15" t="s">
         <v>74</v>
@@ -5718,7 +5234,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13">
       <c r="A8" s="9"/>
       <c r="B8" s="15" t="s">
         <v>75</v>
@@ -5745,7 +5261,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13">
       <c r="A9" s="9"/>
       <c r="B9" s="15" t="s">
         <v>76</v>
@@ -5772,7 +5288,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13">
       <c r="A10" s="9"/>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -5799,7 +5315,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13">
       <c r="A11" s="9"/>
       <c r="B11" s="15" t="s">
         <v>71</v>
@@ -5826,7 +5342,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13">
       <c r="A12" s="9"/>
       <c r="B12" s="15" t="s">
         <v>82</v>
@@ -5853,7 +5369,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13">
       <c r="A13" s="9"/>
       <c r="B13" s="15" t="s">
         <v>85</v>
@@ -5880,7 +5396,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13">
       <c r="A14" s="9"/>
       <c r="B14" s="15" t="s">
         <v>87</v>
@@ -5907,7 +5423,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13">
       <c r="A15" s="9"/>
       <c r="B15" s="15" t="s">
         <v>90</v>
@@ -5934,7 +5450,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13">
       <c r="A16" s="9"/>
       <c r="B16" s="15" t="s">
         <v>93</v>
@@ -5961,7 +5477,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13">
       <c r="A17" s="9"/>
       <c r="B17" s="15" t="s">
         <v>95</v>
@@ -5988,7 +5504,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13">
       <c r="B18" s="15" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +5530,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13">
       <c r="B19" s="15" t="s">
         <v>99</v>
       </c>
@@ -6040,7 +5556,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13">
       <c r="B20" s="15" t="s">
         <v>101</v>
       </c>
@@ -6066,7 +5582,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13">
       <c r="B21" s="15" t="s">
         <v>103</v>
       </c>
@@ -6092,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13">
       <c r="B22" s="15" t="s">
         <v>106</v>
       </c>
@@ -6118,7 +5634,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13">
       <c r="B23" s="15" t="s">
         <v>109</v>
       </c>
@@ -6144,7 +5660,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13">
       <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
@@ -6170,7 +5686,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13">
       <c r="B25" s="15" t="s">
         <v>114</v>
       </c>
@@ -6196,7 +5712,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13">
       <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
@@ -6213,7 +5729,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13">
       <c r="B27" s="15" t="s">
         <v>118</v>
       </c>
@@ -6230,7 +5746,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13">
       <c r="B28" s="15" t="s">
         <v>121</v>
       </c>
@@ -6247,7 +5763,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.5">
+    <row r="29" spans="1:14" ht="13">
       <c r="B29" s="15" t="s">
         <v>123</v>
       </c>
@@ -6264,7 +5780,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.5">
+    <row r="30" spans="1:14" ht="13">
       <c r="B30" s="15" t="s">
         <v>124</v>
       </c>
@@ -6281,7 +5797,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.5">
+    <row r="31" spans="1:14" ht="13">
       <c r="B31" s="15" t="s">
         <v>126</v>
       </c>
@@ -6298,7 +5814,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.5">
+    <row r="32" spans="1:14" ht="13">
       <c r="B32" s="15" t="s">
         <v>128</v>
       </c>
@@ -6315,7 +5831,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.5">
+    <row r="33" spans="2:9" ht="13">
       <c r="B33" s="15" t="s">
         <v>130</v>
       </c>
@@ -6332,7 +5848,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5">
+    <row r="34" spans="2:9" ht="13">
       <c r="B34" s="15" t="s">
         <v>132</v>
       </c>
@@ -6349,7 +5865,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5">
+    <row r="35" spans="2:9" ht="13">
       <c r="B35" s="15" t="s">
         <v>133</v>
       </c>
@@ -6366,7 +5882,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.5">
+    <row r="36" spans="2:9" ht="13">
       <c r="B36" s="15" t="s">
         <v>134</v>
       </c>
@@ -6383,7 +5899,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.5">
+    <row r="37" spans="2:9" ht="13">
       <c r="B37" s="15" t="s">
         <v>135</v>
       </c>
@@ -6400,7 +5916,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.5">
+    <row r="38" spans="2:9" ht="13">
       <c r="B38" s="15" t="s">
         <v>136</v>
       </c>
@@ -6417,7 +5933,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5">
+    <row r="39" spans="2:9" ht="13">
       <c r="B39" s="15" t="s">
         <v>137</v>
       </c>
@@ -6434,7 +5950,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.5">
+    <row r="40" spans="2:9" ht="13">
       <c r="B40" s="15" t="s">
         <v>138</v>
       </c>
@@ -6451,7 +5967,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.5">
+    <row r="41" spans="2:9" ht="13">
       <c r="B41" s="15" t="s">
         <v>139</v>
       </c>
@@ -6468,7 +5984,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.5">
+    <row r="42" spans="2:9" ht="13">
       <c r="B42" s="15" t="s">
         <v>140</v>
       </c>
@@ -6485,7 +6001,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.5">
+    <row r="43" spans="2:9" ht="13">
       <c r="B43" s="15" t="s">
         <v>141</v>
       </c>
@@ -6502,7 +6018,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.5">
+    <row r="44" spans="2:9" ht="13">
       <c r="B44" s="15" t="s">
         <v>142</v>
       </c>
@@ -6519,7 +6035,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.5">
+    <row r="45" spans="2:9" ht="13">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -6536,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.5">
+    <row r="46" spans="2:9" ht="13">
       <c r="B46" s="15" t="s">
         <v>144</v>
       </c>
@@ -6553,7 +6069,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.5">
+    <row r="47" spans="2:9" ht="13">
       <c r="B47" s="15" t="s">
         <v>145</v>
       </c>
@@ -6570,7 +6086,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.5">
+    <row r="48" spans="2:9" ht="13">
       <c r="B48" s="15" t="s">
         <v>146</v>
       </c>
@@ -6587,7 +6103,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.5">
+    <row r="49" spans="2:9" ht="13">
       <c r="B49" s="15" t="s">
         <v>147</v>
       </c>
@@ -6604,7 +6120,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.5">
+    <row r="50" spans="2:9" ht="13">
       <c r="B50" s="15" t="s">
         <v>148</v>
       </c>
@@ -6621,7 +6137,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.5">
+    <row r="51" spans="2:9" ht="13">
       <c r="B51" s="15" t="s">
         <v>149</v>
       </c>
@@ -6641,7 +6157,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.5">
+    <row r="52" spans="2:9" ht="13">
       <c r="B52" s="15" t="s">
         <v>150</v>
       </c>
@@ -6655,7 +6171,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.5">
+    <row r="53" spans="2:9" ht="13">
       <c r="B53" s="15" t="s">
         <v>151</v>
       </c>
@@ -6669,7 +6185,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.5">
+    <row r="54" spans="2:9" ht="13">
       <c r="B54" s="15" t="s">
         <v>152</v>
       </c>
@@ -7135,12 +6651,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="18" thickBot="1">
+    <row r="99" spans="5:10" ht="17.5" thickBot="1">
       <c r="E99" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
       <c r="E100" s="1" t="s">
         <v>48</v>
       </c>
@@ -7160,7 +6676,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="15">
+    <row r="101" spans="5:10" ht="14.5">
       <c r="E101"/>
       <c r="F101" s="17" t="s">
         <v>189</v>
@@ -7176,7 +6692,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="15">
+    <row r="102" spans="5:10" ht="14.5">
       <c r="E102"/>
       <c r="F102" s="17" t="s">
         <v>191</v>
@@ -7196,22 +6712,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="2"/>
-    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="2" width="8.81640625" style="2"/>
+    <col min="3" max="3" width="20.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18" thickBot="1">
+    <row r="3" spans="2:4" ht="17.5" thickBot="1">
       <c r="B3" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="1" t="s">
         <v>50</v>
       </c>
@@ -7398,17 +6914,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" ht="13">
       <c r="B23" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="18" thickBot="1">
+    <row r="25" spans="2:4" ht="17.5" thickBot="1">
       <c r="B25" s="16" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B26" s="1" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF3DCCF-7DE9-48F6-9043-3B892946F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FC82F3-C084-498C-B7C6-C87643E275C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="289">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -874,7 +874,37 @@
     <t>elc_spv_viljandi</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster Viljandi</t>
+    <t>elc_spv_ida_viru</t>
+  </si>
+  <si>
+    <t>elc_spv_jarva</t>
+  </si>
+  <si>
+    <t>elc_spv_jogeva</t>
+  </si>
+  <si>
+    <t>elc_spv_polva</t>
+  </si>
+  <si>
+    <t>elc_spv_valga</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Valga</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Viljandi</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Ida-Viru</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Jarva</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Jogeva</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Polva</t>
   </si>
 </sst>
 </file>
@@ -3308,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R44"/>
+  <dimension ref="B3:R42"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -3322,6 +3352,7 @@
     <col min="14" max="14" width="17.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="45.7265625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:18" ht="17.5" thickBot="1">
@@ -3488,10 +3519,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="O8" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3517,10 +3548,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O9" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3546,10 +3577,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="O10" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3575,10 +3606,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -3604,10 +3635,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="O12" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -3633,10 +3664,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -3665,10 +3696,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -3697,10 +3728,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="O15" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3738,10 +3769,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="O16" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3770,10 +3801,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -3802,10 +3833,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O18" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -3834,10 +3865,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -3866,10 +3897,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -3898,10 +3929,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -3936,10 +3967,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="O22" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -3968,10 +3999,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -3997,10 +4028,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4026,10 +4057,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4046,10 +4077,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4066,10 +4097,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -4086,10 +4117,10 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -4106,10 +4137,10 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -4118,6 +4149,146 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>255</v>
+      </c>
+      <c r="O30" t="s">
+        <v>256</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>257</v>
+      </c>
+      <c r="O31" t="s">
+        <v>258</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>259</v>
+      </c>
+      <c r="O32" t="s">
+        <v>260</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>261</v>
+      </c>
+      <c r="O33" t="s">
+        <v>262</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>263</v>
+      </c>
+      <c r="O34" t="s">
+        <v>264</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>215</v>
+      </c>
+      <c r="O38" t="s">
+        <v>216</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>217</v>
+      </c>
+      <c r="O39" t="s">
+        <v>218</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4126,10 +4297,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4146,10 +4317,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O41" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4166,10 +4337,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O42" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -4178,46 +4349,6 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="43" spans="13:18">
-      <c r="M43" t="s">
-        <v>17</v>
-      </c>
-      <c r="N43" t="s">
-        <v>221</v>
-      </c>
-      <c r="O43" t="s">
-        <v>222</v>
-      </c>
-      <c r="P43" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>35</v>
-      </c>
-      <c r="R43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="44" spans="13:18">
-      <c r="M44" t="s">
-        <v>17</v>
-      </c>
-      <c r="N44" t="s">
-        <v>223</v>
-      </c>
-      <c r="O44" t="s">
-        <v>224</v>
-      </c>
-      <c r="P44" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>35</v>
-      </c>
-      <c r="R44" t="s">
         <v>214</v>
       </c>
     </row>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FC82F3-C084-498C-B7C6-C87643E275C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788F60B9-9F8B-4B72-92B2-F845D23A01F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="263">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -685,156 +685,6 @@
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 4</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 5</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 6</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 7</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 9</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 1</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 2</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 3</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 4</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 5</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 6</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 7</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 8</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 9</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>wind offshore electricity generation in cluster -- 10</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 1</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 2</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 3</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 4</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 5</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 6</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 7</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 8</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 9</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 10</t>
-  </si>
-  <si>
     <t>PDef1</t>
   </si>
   <si>
@@ -905,6 +755,78 @@
   </si>
   <si>
     <t>solar electricity generation in Polva</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Parnu</t>
+  </si>
+  <si>
+    <t>Parnu</t>
+  </si>
+  <si>
+    <t>Tartu</t>
+  </si>
+  <si>
+    <t>Laane-Viru</t>
+  </si>
+  <si>
+    <t>Ida-Viru</t>
+  </si>
+  <si>
+    <t>Jarva</t>
+  </si>
+  <si>
+    <t>Jogeva</t>
+  </si>
+  <si>
+    <t>Polva</t>
+  </si>
+  <si>
+    <t>Valga</t>
+  </si>
+  <si>
+    <t>Viljandi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onshore wind electricity generation in </t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Laane-Viru</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Ida-Viru</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Jarva</t>
+  </si>
+  <si>
+    <t>elc_won_parnu</t>
+  </si>
+  <si>
+    <t>elc_won_saaremaa</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Saaremaa</t>
+  </si>
+  <si>
+    <t>elc_won_laane_viru</t>
+  </si>
+  <si>
+    <t>elc_won_ida_viru</t>
+  </si>
+  <si>
+    <t>elc_won_laanemaa</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in Harju</t>
+  </si>
+  <si>
+    <t>elc_won_harju</t>
+  </si>
+  <si>
+    <t>elc_wof_parnu_laht</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in Gulf of Parnu</t>
   </si>
 </sst>
 </file>
@@ -3338,7 +3260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R42"/>
+  <dimension ref="B3:W37"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -3355,7 +3277,7 @@
     <col min="20" max="20" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.5" thickBot="1">
+    <row r="3" spans="2:23" ht="17.5" thickBot="1">
       <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
@@ -3374,7 +3296,7 @@
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="2:18" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:23" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
@@ -3417,8 +3339,18 @@
       <c r="R4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="2:18">
+      <c r="U4" t="str">
+        <f>LOWER(V4)</f>
+        <v>parnu</v>
+      </c>
+      <c r="V4" t="s">
+        <v>240</v>
+      </c>
+      <c r="W4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -3432,10 +3364,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="O5" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3446,8 +3378,15 @@
       <c r="R5" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="6" spans="2:18">
+      <c r="U5" t="str">
+        <f t="shared" ref="U5:U11" si="0">LOWER(V5)</f>
+        <v>tartu</v>
+      </c>
+      <c r="V5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23">
       <c r="B6" t="s">
         <v>17</v>
       </c>
@@ -3461,10 +3400,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3475,8 +3414,15 @@
       <c r="R6" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="7" spans="2:18">
+      <c r="U6" t="str">
+        <f t="shared" si="0"/>
+        <v>laane-viru</v>
+      </c>
+      <c r="V6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -3490,10 +3436,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="O7" t="s">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3504,8 +3450,15 @@
       <c r="R7" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="8" spans="2:18">
+      <c r="U7" t="str">
+        <f t="shared" si="0"/>
+        <v>ida-viru</v>
+      </c>
+      <c r="V7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -3519,10 +3472,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>278</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3533,8 +3486,15 @@
       <c r="R8" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="9" spans="2:18">
+      <c r="U8" t="str">
+        <f t="shared" si="0"/>
+        <v>jarva</v>
+      </c>
+      <c r="V8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -3548,10 +3508,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="O9" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3562,8 +3522,15 @@
       <c r="R9" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="10" spans="2:18">
+      <c r="U9" t="str">
+        <f t="shared" si="0"/>
+        <v>jogeva</v>
+      </c>
+      <c r="V9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -3577,10 +3544,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="O10" t="s">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3591,8 +3558,15 @@
       <c r="R10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="11" spans="2:18">
+      <c r="U10" t="str">
+        <f t="shared" si="0"/>
+        <v>polva</v>
+      </c>
+      <c r="V10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -3606,10 +3580,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="O11" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -3620,8 +3594,15 @@
       <c r="R11" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="12" spans="2:18">
+      <c r="U11" t="str">
+        <f t="shared" si="0"/>
+        <v>valga</v>
+      </c>
+      <c r="V11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -3635,10 +3616,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="O12" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -3649,8 +3630,15 @@
       <c r="R12" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="13" spans="2:18">
+      <c r="U12" t="str">
+        <f>LOWER(V12)</f>
+        <v>viljandi</v>
+      </c>
+      <c r="V12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23">
       <c r="B13" t="s">
         <v>17</v>
       </c>
@@ -3664,10 +3652,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
-        <v>283</v>
+        <v>233</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -3679,7 +3667,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="2:18">
+    <row r="14" spans="2:23">
       <c r="B14" t="s">
         <v>17</v>
       </c>
@@ -3696,10 +3684,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="O14" t="s">
-        <v>284</v>
+        <v>234</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -3711,7 +3699,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="2:18">
+    <row r="15" spans="2:23">
       <c r="B15" t="s">
         <v>17</v>
       </c>
@@ -3728,10 +3716,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="O15" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3743,7 +3731,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="2:18">
+    <row r="16" spans="2:23">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -3769,10 +3757,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="O16" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3784,7 +3772,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="2:18">
+    <row r="17" spans="2:22">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3801,10 +3789,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="O17" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -3816,7 +3804,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="2:18">
+    <row r="18" spans="2:22">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3833,10 +3821,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="O18" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -3848,7 +3836,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="2:18">
+    <row r="19" spans="2:22">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3865,10 +3853,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="O19" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -3879,16 +3867,20 @@
       <c r="R19" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" spans="2:18">
+      <c r="V19" t="str">
+        <f>"onshore wind electricity generation in " &amp;V5</f>
+        <v>onshore wind electricity generation in Tartu</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D20" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3897,10 +3889,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="O20" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -3911,8 +3903,12 @@
       <c r="R20" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="21" spans="2:18">
+      <c r="V20" t="str">
+        <f>"onshore wind electricity generation in " &amp;V6</f>
+        <v>onshore wind electricity generation in Laane-Viru</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
       <c r="B21" t="s">
         <v>34</v>
       </c>
@@ -3929,10 +3925,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="O21" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -3943,8 +3939,12 @@
       <c r="R21" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="22" spans="2:18">
+      <c r="V21" t="str">
+        <f>"onshore wind electricity generation in " &amp;V7</f>
+        <v>onshore wind electricity generation in Ida-Viru</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -3963,26 +3963,12 @@
       <c r="G22" t="s">
         <v>25</v>
       </c>
-      <c r="M22" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" t="s">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s">
-        <v>240</v>
-      </c>
-      <c r="P22" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18">
+      <c r="V22" t="str">
+        <f>"onshore wind electricity generation in " &amp;V8</f>
+        <v>onshore wind electricity generation in Jarva</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
       <c r="B23" t="s">
         <v>192</v>
       </c>
@@ -3995,26 +3981,12 @@
       <c r="E23" t="s">
         <v>195</v>
       </c>
-      <c r="M23" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" t="s">
-        <v>241</v>
-      </c>
-      <c r="O23" t="s">
-        <v>242</v>
-      </c>
-      <c r="P23" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>35</v>
-      </c>
-      <c r="R23" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18">
+      <c r="V23" t="str">
+        <f>"onshore wind electricity generation in " &amp;V9</f>
+        <v>onshore wind electricity generation in Jogeva</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
       <c r="B24" t="s">
         <v>192</v>
       </c>
@@ -4024,26 +3996,12 @@
       <c r="E24" t="s">
         <v>195</v>
       </c>
-      <c r="M24" t="s">
-        <v>17</v>
-      </c>
-      <c r="N24" t="s">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s">
-        <v>244</v>
-      </c>
-      <c r="P24" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>35</v>
-      </c>
-      <c r="R24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18">
+      <c r="V24" t="str">
+        <f>"onshore wind electricity generation in " &amp;V10</f>
+        <v>onshore wind electricity generation in Polva</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
       <c r="B25" t="s">
         <v>192</v>
       </c>
@@ -4053,303 +4011,69 @@
       <c r="E25" t="s">
         <v>195</v>
       </c>
-      <c r="M25" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" t="s">
-        <v>245</v>
-      </c>
-      <c r="O25" t="s">
-        <v>246</v>
-      </c>
-      <c r="P25" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>35</v>
-      </c>
-      <c r="R25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18">
-      <c r="M26" t="s">
-        <v>17</v>
-      </c>
-      <c r="N26" t="s">
-        <v>247</v>
-      </c>
-      <c r="O26" t="s">
-        <v>248</v>
-      </c>
-      <c r="P26" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18">
-      <c r="M27" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" t="s">
-        <v>249</v>
-      </c>
-      <c r="O27" t="s">
-        <v>250</v>
-      </c>
-      <c r="P27" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>35</v>
-      </c>
-      <c r="R27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>251</v>
-      </c>
-      <c r="O28" t="s">
-        <v>252</v>
-      </c>
-      <c r="P28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>253</v>
-      </c>
-      <c r="O29" t="s">
-        <v>254</v>
-      </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="M30" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" t="s">
-        <v>255</v>
-      </c>
-      <c r="O30" t="s">
-        <v>256</v>
-      </c>
-      <c r="P30" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>35</v>
-      </c>
-      <c r="R30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18">
-      <c r="M31" t="s">
-        <v>17</v>
-      </c>
-      <c r="N31" t="s">
-        <v>257</v>
-      </c>
-      <c r="O31" t="s">
-        <v>258</v>
-      </c>
-      <c r="P31" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>35</v>
-      </c>
-      <c r="R31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18">
-      <c r="M32" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" t="s">
-        <v>259</v>
-      </c>
-      <c r="O32" t="s">
-        <v>260</v>
-      </c>
-      <c r="P32" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="13:18">
-      <c r="M33" t="s">
-        <v>17</v>
-      </c>
-      <c r="N33" t="s">
-        <v>261</v>
-      </c>
-      <c r="O33" t="s">
-        <v>262</v>
-      </c>
-      <c r="P33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="13:18">
-      <c r="M34" t="s">
-        <v>17</v>
-      </c>
-      <c r="N34" t="s">
-        <v>263</v>
-      </c>
-      <c r="O34" t="s">
-        <v>264</v>
-      </c>
-      <c r="P34" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" spans="13:18">
-      <c r="M38" t="s">
-        <v>17</v>
-      </c>
-      <c r="N38" t="s">
-        <v>215</v>
-      </c>
-      <c r="O38" t="s">
-        <v>216</v>
-      </c>
-      <c r="P38" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="39" spans="13:18">
-      <c r="M39" t="s">
-        <v>17</v>
-      </c>
-      <c r="N39" t="s">
-        <v>217</v>
-      </c>
-      <c r="O39" t="s">
-        <v>218</v>
-      </c>
-      <c r="P39" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>35</v>
-      </c>
-      <c r="R39" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="40" spans="13:18">
-      <c r="M40" t="s">
-        <v>17</v>
-      </c>
-      <c r="N40" t="s">
-        <v>219</v>
-      </c>
-      <c r="O40" t="s">
-        <v>220</v>
-      </c>
-      <c r="P40" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>35</v>
-      </c>
-      <c r="R40" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="41" spans="13:18">
-      <c r="M41" t="s">
-        <v>17</v>
-      </c>
-      <c r="N41" t="s">
-        <v>221</v>
-      </c>
-      <c r="O41" t="s">
-        <v>222</v>
-      </c>
-      <c r="P41" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>35</v>
-      </c>
-      <c r="R41" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="42" spans="13:18">
-      <c r="M42" t="s">
-        <v>17</v>
-      </c>
-      <c r="N42" t="s">
-        <v>223</v>
-      </c>
-      <c r="O42" t="s">
-        <v>224</v>
-      </c>
-      <c r="P42" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42" t="s">
-        <v>214</v>
+      <c r="V25" t="str">
+        <f t="shared" ref="V25:V26" si="1">"onshore wind electricity generation in " &amp;V11</f>
+        <v>onshore wind electricity generation in Valga</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="V26" t="str">
+        <f t="shared" si="1"/>
+        <v>onshore wind electricity generation in Viljandi</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="V29" t="str">
+        <f>"elc_won_"&amp;U4</f>
+        <v>elc_won_parnu</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="V30" t="str">
+        <f t="shared" ref="V30:V36" si="2">"elc_won_"&amp;U5</f>
+        <v>elc_won_tartu</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="V31" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_laane-viru</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22">
+      <c r="V32" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_ida-viru</v>
+      </c>
+    </row>
+    <row r="33" spans="22:22">
+      <c r="V33" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_jarva</v>
+      </c>
+    </row>
+    <row r="34" spans="22:22">
+      <c r="V34" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_jogeva</v>
+      </c>
+    </row>
+    <row r="35" spans="22:22">
+      <c r="V35" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_polva</v>
+      </c>
+    </row>
+    <row r="36" spans="22:22">
+      <c r="V36" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_won_valga</v>
+      </c>
+    </row>
+    <row r="37" spans="22:22">
+      <c r="V37" t="str">
+        <f>"elc_won_"&amp;U12</f>
+        <v>elc_won_viljandi</v>
       </c>
     </row>
   </sheetData>
@@ -4391,7 +4115,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="2" t="s">
-        <v>268</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -4404,7 +4128,7 @@
     </row>
     <row r="12" spans="2:7" ht="14.5">
       <c r="B12" s="3" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788F60B9-9F8B-4B72-92B2-F845D23A01F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7901D393-71BC-4F76-843F-C7CFF15B21B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="273">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -827,6 +827,36 @@
   </si>
   <si>
     <t>wind offshore electricity generation in Gulf of Parnu</t>
+  </si>
+  <si>
+    <t>elc_spv_voru</t>
+  </si>
+  <si>
+    <t>elc_spv_saare</t>
+  </si>
+  <si>
+    <t>elc_spv_rapla</t>
+  </si>
+  <si>
+    <t>elv_spv_laane</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Voru</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Saare</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Rapla</t>
+  </si>
+  <si>
+    <t>solar electricity generation in Laane</t>
+  </si>
+  <si>
+    <t>solar electricity generation in hiiu</t>
+  </si>
+  <si>
+    <t>elv_spv_hiiu</t>
   </si>
 </sst>
 </file>
@@ -3186,15 +3216,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3261,23 +3291,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:W37"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="45.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" ht="17.5" thickBot="1">
+    <row r="3" spans="2:23" ht="18" thickBot="1">
       <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
@@ -3296,7 +3326,7 @@
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="2:23" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:23" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
@@ -3716,10 +3746,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O15" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3757,10 +3787,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3789,10 +3819,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O17" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -3821,10 +3851,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="O18" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -3853,10 +3883,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="O19" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -3868,7 +3898,7 @@
         <v>214</v>
       </c>
       <c r="V19" t="str">
-        <f>"onshore wind electricity generation in " &amp;V5</f>
+        <f t="shared" ref="V19:V24" si="1">"onshore wind electricity generation in " &amp;V5</f>
         <v>onshore wind electricity generation in Tartu</v>
       </c>
     </row>
@@ -3889,10 +3919,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="O20" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -3904,7 +3934,7 @@
         <v>214</v>
       </c>
       <c r="V20" t="str">
-        <f>"onshore wind electricity generation in " &amp;V6</f>
+        <f t="shared" si="1"/>
         <v>onshore wind electricity generation in Laane-Viru</v>
       </c>
     </row>
@@ -3925,10 +3955,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -3940,7 +3970,7 @@
         <v>214</v>
       </c>
       <c r="V21" t="str">
-        <f>"onshore wind electricity generation in " &amp;V7</f>
+        <f t="shared" si="1"/>
         <v>onshore wind electricity generation in Ida-Viru</v>
       </c>
     </row>
@@ -3963,8 +3993,26 @@
       <c r="G22" t="s">
         <v>25</v>
       </c>
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>256</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>214</v>
+      </c>
       <c r="V22" t="str">
-        <f>"onshore wind electricity generation in " &amp;V8</f>
+        <f t="shared" si="1"/>
         <v>onshore wind electricity generation in Jarva</v>
       </c>
     </row>
@@ -3981,8 +4029,26 @@
       <c r="E23" t="s">
         <v>195</v>
       </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>257</v>
+      </c>
+      <c r="O23" t="s">
+        <v>251</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>214</v>
+      </c>
       <c r="V23" t="str">
-        <f>"onshore wind electricity generation in " &amp;V9</f>
+        <f t="shared" si="1"/>
         <v>onshore wind electricity generation in Jogeva</v>
       </c>
     </row>
@@ -3996,8 +4062,26 @@
       <c r="E24" t="s">
         <v>195</v>
       </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>258</v>
+      </c>
+      <c r="O24" t="s">
+        <v>252</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>214</v>
+      </c>
       <c r="V24" t="str">
-        <f>"onshore wind electricity generation in " &amp;V10</f>
+        <f t="shared" si="1"/>
         <v>onshore wind electricity generation in Polva</v>
       </c>
     </row>
@@ -4011,14 +4095,50 @@
       <c r="E25" t="s">
         <v>195</v>
       </c>
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>254</v>
+      </c>
+      <c r="O25" t="s">
+        <v>255</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>214</v>
+      </c>
       <c r="V25" t="str">
-        <f t="shared" ref="V25:V26" si="1">"onshore wind electricity generation in " &amp;V11</f>
+        <f t="shared" ref="V25:V26" si="2">"onshore wind electricity generation in " &amp;V11</f>
         <v>onshore wind electricity generation in Valga</v>
       </c>
     </row>
     <row r="26" spans="2:22">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>260</v>
+      </c>
+      <c r="O26" t="s">
+        <v>259</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>214</v>
+      </c>
       <c r="V26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>onshore wind electricity generation in Viljandi</v>
       </c>
     </row>
@@ -4030,43 +4150,43 @@
     </row>
     <row r="30" spans="2:22">
       <c r="V30" t="str">
-        <f t="shared" ref="V30:V36" si="2">"elc_won_"&amp;U5</f>
+        <f t="shared" ref="V30:V36" si="3">"elc_won_"&amp;U5</f>
         <v>elc_won_tartu</v>
       </c>
     </row>
     <row r="31" spans="2:22">
       <c r="V31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_laane-viru</v>
       </c>
     </row>
     <row r="32" spans="2:22">
       <c r="V32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_ida-viru</v>
       </c>
     </row>
     <row r="33" spans="22:22">
       <c r="V33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_jarva</v>
       </c>
     </row>
     <row r="34" spans="22:22">
       <c r="V34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_jogeva</v>
       </c>
     </row>
     <row r="35" spans="22:22">
       <c r="V35" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_polva</v>
       </c>
     </row>
     <row r="36" spans="22:22">
       <c r="V36" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elc_won_valga</v>
       </c>
     </row>
@@ -4087,15 +4207,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="2"/>
-    <col min="4" max="4" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="2"/>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="2"/>
+    <col min="4" max="4" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4126,7 +4246,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.5">
+    <row r="12" spans="2:7" ht="15">
       <c r="B12" s="3" t="s">
         <v>215</v>
       </c>
@@ -4146,7 +4266,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.5">
+    <row r="13" spans="2:7" ht="15">
       <c r="B13" s="5">
         <v>1</v>
       </c>
@@ -4154,7 +4274,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.5">
+    <row r="14" spans="2:7" ht="15">
       <c r="B14" s="5">
         <v>5</v>
       </c>
@@ -4173,7 +4293,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.5">
+    <row r="15" spans="2:7" ht="15">
       <c r="B15" s="5">
         <v>5</v>
       </c>
@@ -4192,7 +4312,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.5">
+    <row r="16" spans="2:7" ht="15">
       <c r="B16" s="5">
         <v>5</v>
       </c>
@@ -4211,7 +4331,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.5">
+    <row r="17" spans="2:7" ht="15">
       <c r="B17" s="5">
         <v>5</v>
       </c>
@@ -4230,7 +4350,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.5">
+    <row r="18" spans="2:7" ht="15">
       <c r="B18" s="5">
         <v>5</v>
       </c>
@@ -4249,7 +4369,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.5">
+    <row r="19" spans="2:7" ht="15">
       <c r="B19" s="5">
         <v>5</v>
       </c>
@@ -4264,7 +4384,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.5">
+    <row r="20" spans="2:7" ht="15">
       <c r="B20" s="5"/>
       <c r="D20" s="2" t="s">
         <v>46</v>
@@ -4274,70 +4394,70 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.5">
+    <row r="21" spans="2:7" ht="15">
       <c r="B21" s="5"/>
       <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.5">
+    <row r="22" spans="2:7" ht="15">
       <c r="B22" s="5"/>
       <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.5">
+    <row r="23" spans="2:7" ht="15">
       <c r="B23" s="5"/>
       <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.5">
+    <row r="24" spans="2:7" ht="15">
       <c r="B24" s="5"/>
       <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.5">
+    <row r="25" spans="2:7" ht="15">
       <c r="B25" s="5"/>
       <c r="D25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.5">
+    <row r="26" spans="2:7" ht="15">
       <c r="B26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.5">
+    <row r="27" spans="2:7" ht="15">
       <c r="B27" s="5"/>
       <c r="D27" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.5">
+    <row r="28" spans="2:7" ht="15">
       <c r="B28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.5">
+    <row r="29" spans="2:7" ht="15">
       <c r="B29" s="5"/>
       <c r="D29" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.5">
+    <row r="30" spans="2:7" ht="15">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="2:7" ht="14.5">
+    <row r="31" spans="2:7" ht="15">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="2:7" ht="14.5">
+    <row r="32" spans="2:7" ht="15">
       <c r="B32" s="5"/>
     </row>
-    <row r="33" spans="2:2" ht="14.5">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="5"/>
     </row>
   </sheetData>
@@ -4349,28 +4469,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="7"/>
-    <col min="2" max="2" width="8.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="2" max="2" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.453125" style="7"/>
+    <col min="9" max="9" width="6.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.5">
+    <row r="1" spans="2:12" ht="12.75">
       <c r="B1" s="2"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="2:12" ht="12.5">
+    <row r="2" spans="2:12" ht="12.75">
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4381,7 +4501,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="2:12" ht="12.5">
+    <row r="3" spans="2:12" ht="12.75">
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
@@ -4400,7 +4520,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="2:12" ht="12">
+    <row r="5" spans="2:12">
       <c r="B5" s="11" t="s">
         <v>48</v>
       </c>
@@ -4509,7 +4629,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="2:12" ht="12">
+    <row r="15" spans="2:12">
       <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
@@ -4557,7 +4677,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.5">
+    <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -4568,7 +4688,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="2:14" ht="12.5">
+    <row r="19" spans="2:14" ht="12.75">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -4579,7 +4699,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="2:14" ht="12.5">
+    <row r="20" spans="2:14" ht="12.75">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -4590,7 +4710,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="2:14" ht="14.5">
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4605,7 +4725,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.5">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4620,7 +4740,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.5">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4635,7 +4755,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.5">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4650,7 +4770,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.5">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4665,7 +4785,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.5">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4680,7 +4800,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.5">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4695,7 +4815,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.5">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4710,7 +4830,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.5">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4725,7 +4845,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.5">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4740,7 +4860,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.5">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4755,7 +4875,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.5">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4770,7 +4890,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.5">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4785,7 +4905,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.5">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4800,7 +4920,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.5">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4815,7 +4935,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.5">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4830,7 +4950,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.5">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4845,7 +4965,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.5">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4860,7 +4980,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.5">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -4875,7 +4995,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.5">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -4890,7 +5010,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.5">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -4905,7 +5025,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.5">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -4930,25 +5050,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="7"/>
-    <col min="2" max="2" width="12.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.453125" style="7"/>
-    <col min="5" max="5" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="2" max="2" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="7"/>
+    <col min="5" max="5" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="7"/>
-    <col min="12" max="12" width="17.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.453125" style="7"/>
+    <col min="10" max="10" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="7"/>
+    <col min="12" max="12" width="17.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.5" thickBot="1">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
       <c r="A2" s="9"/>
       <c r="B2" s="16" t="s">
         <v>68</v>
@@ -4962,7 +5082,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="1" t="s">
         <v>70</v>
@@ -4995,7 +5115,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13">
+    <row r="4" spans="1:14" ht="13.5">
       <c r="A4" s="9"/>
       <c r="B4" s="15" t="s">
         <v>134</v>
@@ -5020,7 +5140,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13">
+    <row r="5" spans="1:14" ht="13.5">
       <c r="A5" s="9"/>
       <c r="B5" s="15" t="s">
         <v>72</v>
@@ -5047,7 +5167,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13">
+    <row r="6" spans="1:14" ht="13.5">
       <c r="A6" s="9"/>
       <c r="B6" s="15" t="s">
         <v>73</v>
@@ -5068,7 +5188,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13">
+    <row r="7" spans="1:14" ht="13.5">
       <c r="A7" s="9"/>
       <c r="B7" s="15" t="s">
         <v>74</v>
@@ -5089,7 +5209,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13">
+    <row r="8" spans="1:14" ht="13.5">
       <c r="A8" s="9"/>
       <c r="B8" s="15" t="s">
         <v>75</v>
@@ -5116,7 +5236,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13">
+    <row r="9" spans="1:14" ht="13.5">
       <c r="A9" s="9"/>
       <c r="B9" s="15" t="s">
         <v>76</v>
@@ -5143,7 +5263,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13">
+    <row r="10" spans="1:14" ht="13.5">
       <c r="A10" s="9"/>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -5170,7 +5290,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13">
+    <row r="11" spans="1:14" ht="13.5">
       <c r="A11" s="9"/>
       <c r="B11" s="15" t="s">
         <v>71</v>
@@ -5197,7 +5317,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13">
+    <row r="12" spans="1:14" ht="13.5">
       <c r="A12" s="9"/>
       <c r="B12" s="15" t="s">
         <v>82</v>
@@ -5224,7 +5344,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13">
+    <row r="13" spans="1:14" ht="13.5">
       <c r="A13" s="9"/>
       <c r="B13" s="15" t="s">
         <v>85</v>
@@ -5251,7 +5371,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13">
+    <row r="14" spans="1:14" ht="13.5">
       <c r="A14" s="9"/>
       <c r="B14" s="15" t="s">
         <v>87</v>
@@ -5278,7 +5398,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13">
+    <row r="15" spans="1:14" ht="13.5">
       <c r="A15" s="9"/>
       <c r="B15" s="15" t="s">
         <v>90</v>
@@ -5305,7 +5425,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13">
+    <row r="16" spans="1:14" ht="13.5">
       <c r="A16" s="9"/>
       <c r="B16" s="15" t="s">
         <v>93</v>
@@ -5332,7 +5452,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13">
+    <row r="17" spans="1:14" ht="13.5">
       <c r="A17" s="9"/>
       <c r="B17" s="15" t="s">
         <v>95</v>
@@ -5359,7 +5479,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13">
+    <row r="18" spans="1:14" ht="13.5">
       <c r="B18" s="15" t="s">
         <v>97</v>
       </c>
@@ -5385,7 +5505,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13">
+    <row r="19" spans="1:14" ht="13.5">
       <c r="B19" s="15" t="s">
         <v>99</v>
       </c>
@@ -5411,7 +5531,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13">
+    <row r="20" spans="1:14" ht="13.5">
       <c r="B20" s="15" t="s">
         <v>101</v>
       </c>
@@ -5437,7 +5557,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13">
+    <row r="21" spans="1:14" ht="13.5">
       <c r="B21" s="15" t="s">
         <v>103</v>
       </c>
@@ -5463,7 +5583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13">
+    <row r="22" spans="1:14" ht="13.5">
       <c r="B22" s="15" t="s">
         <v>106</v>
       </c>
@@ -5489,7 +5609,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13">
+    <row r="23" spans="1:14" ht="13.5">
       <c r="B23" s="15" t="s">
         <v>109</v>
       </c>
@@ -5515,7 +5635,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13">
+    <row r="24" spans="1:14" ht="13.5">
       <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
@@ -5541,7 +5661,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13">
+    <row r="25" spans="1:14" ht="13.5">
       <c r="B25" s="15" t="s">
         <v>114</v>
       </c>
@@ -5567,7 +5687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13">
+    <row r="26" spans="1:14" ht="13.5">
       <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
@@ -5584,7 +5704,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13">
+    <row r="27" spans="1:14" ht="13.5">
       <c r="B27" s="15" t="s">
         <v>118</v>
       </c>
@@ -5601,7 +5721,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13">
+    <row r="28" spans="1:14" ht="13.5">
       <c r="B28" s="15" t="s">
         <v>121</v>
       </c>
@@ -5618,7 +5738,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13">
+    <row r="29" spans="1:14" ht="13.5">
       <c r="B29" s="15" t="s">
         <v>123</v>
       </c>
@@ -5635,7 +5755,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13">
+    <row r="30" spans="1:14" ht="13.5">
       <c r="B30" s="15" t="s">
         <v>124</v>
       </c>
@@ -5652,7 +5772,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13">
+    <row r="31" spans="1:14" ht="13.5">
       <c r="B31" s="15" t="s">
         <v>126</v>
       </c>
@@ -5669,7 +5789,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13">
+    <row r="32" spans="1:14" ht="13.5">
       <c r="B32" s="15" t="s">
         <v>128</v>
       </c>
@@ -5686,7 +5806,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13">
+    <row r="33" spans="2:9" ht="13.5">
       <c r="B33" s="15" t="s">
         <v>130</v>
       </c>
@@ -5703,7 +5823,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13">
+    <row r="34" spans="2:9" ht="13.5">
       <c r="B34" s="15" t="s">
         <v>132</v>
       </c>
@@ -5720,7 +5840,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13">
+    <row r="35" spans="2:9" ht="13.5">
       <c r="B35" s="15" t="s">
         <v>133</v>
       </c>
@@ -5737,7 +5857,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13">
+    <row r="36" spans="2:9" ht="13.5">
       <c r="B36" s="15" t="s">
         <v>134</v>
       </c>
@@ -5754,7 +5874,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13">
+    <row r="37" spans="2:9" ht="13.5">
       <c r="B37" s="15" t="s">
         <v>135</v>
       </c>
@@ -5771,7 +5891,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13">
+    <row r="38" spans="2:9" ht="13.5">
       <c r="B38" s="15" t="s">
         <v>136</v>
       </c>
@@ -5788,7 +5908,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13">
+    <row r="39" spans="2:9" ht="13.5">
       <c r="B39" s="15" t="s">
         <v>137</v>
       </c>
@@ -5805,7 +5925,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13">
+    <row r="40" spans="2:9" ht="13.5">
       <c r="B40" s="15" t="s">
         <v>138</v>
       </c>
@@ -5822,7 +5942,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13">
+    <row r="41" spans="2:9" ht="13.5">
       <c r="B41" s="15" t="s">
         <v>139</v>
       </c>
@@ -5839,7 +5959,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13">
+    <row r="42" spans="2:9" ht="13.5">
       <c r="B42" s="15" t="s">
         <v>140</v>
       </c>
@@ -5856,7 +5976,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13">
+    <row r="43" spans="2:9" ht="13.5">
       <c r="B43" s="15" t="s">
         <v>141</v>
       </c>
@@ -5873,7 +5993,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13">
+    <row r="44" spans="2:9" ht="13.5">
       <c r="B44" s="15" t="s">
         <v>142</v>
       </c>
@@ -5890,7 +6010,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13">
+    <row r="45" spans="2:9" ht="13.5">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -5907,7 +6027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13">
+    <row r="46" spans="2:9" ht="13.5">
       <c r="B46" s="15" t="s">
         <v>144</v>
       </c>
@@ -5924,7 +6044,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13">
+    <row r="47" spans="2:9" ht="13.5">
       <c r="B47" s="15" t="s">
         <v>145</v>
       </c>
@@ -5941,7 +6061,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13">
+    <row r="48" spans="2:9" ht="13.5">
       <c r="B48" s="15" t="s">
         <v>146</v>
       </c>
@@ -5958,7 +6078,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13">
+    <row r="49" spans="2:9" ht="13.5">
       <c r="B49" s="15" t="s">
         <v>147</v>
       </c>
@@ -5975,7 +6095,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13">
+    <row r="50" spans="2:9" ht="13.5">
       <c r="B50" s="15" t="s">
         <v>148</v>
       </c>
@@ -5992,7 +6112,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13">
+    <row r="51" spans="2:9" ht="13.5">
       <c r="B51" s="15" t="s">
         <v>149</v>
       </c>
@@ -6012,7 +6132,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13">
+    <row r="52" spans="2:9" ht="13.5">
       <c r="B52" s="15" t="s">
         <v>150</v>
       </c>
@@ -6026,7 +6146,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13">
+    <row r="53" spans="2:9" ht="13.5">
       <c r="B53" s="15" t="s">
         <v>151</v>
       </c>
@@ -6040,7 +6160,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13">
+    <row r="54" spans="2:9" ht="13.5">
       <c r="B54" s="15" t="s">
         <v>152</v>
       </c>
@@ -6506,12 +6626,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.5" thickBot="1">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
       <c r="E99" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="E100" s="1" t="s">
         <v>48</v>
       </c>
@@ -6531,7 +6651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.5">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
       <c r="F101" s="17" t="s">
         <v>189</v>
@@ -6547,7 +6667,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.5">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
       <c r="F102" s="17" t="s">
         <v>191</v>
@@ -6570,19 +6690,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.81640625" style="2"/>
-    <col min="3" max="3" width="20.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.81640625" style="2"/>
+    <col min="1" max="2" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.5" thickBot="1">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
       <c r="B3" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="1" t="s">
         <v>50</v>
       </c>
@@ -6769,17 +6889,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="13">
+    <row r="23" spans="2:4">
       <c r="B23" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.5" thickBot="1">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
       <c r="B25" s="16" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B26" s="1" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7901D393-71BC-4F76-843F-C7CFF15B21B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407DA071-CE15-478A-955B-B7C199FDA722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="274">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -857,6 +857,9 @@
   </si>
   <si>
     <t>elv_spv_hiiu</t>
+  </si>
+  <si>
+    <t>EUR25</t>
   </si>
 </sst>
 </file>
@@ -5049,7 +5052,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
-  <dimension ref="A2:N102"/>
+  <dimension ref="A2:N104"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="7"/>
@@ -6681,6 +6684,31 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
+    <row r="103" spans="5:10">
+      <c r="F103" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="I103" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="5:10">
+      <c r="F104" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="I104" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407DA071-CE15-478A-955B-B7C199FDA722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BCE740-1FC3-4995-904A-24B1258FCF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="274">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -6178,6 +6178,9 @@
       </c>
     </row>
     <row r="55" spans="2:9">
+      <c r="B55" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="F55" s="7" t="s">
         <v>191</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BCE740-1FC3-4995-904A-24B1258FCF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887B6AC6-CE14-4411-B244-BD698AC8412D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6689,27 +6689,27 @@
     </row>
     <row r="103" spans="5:10">
       <c r="F103" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>273</v>
       </c>
       <c r="I103" s="7">
-        <v>7.0000000000000007E-2</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="104" spans="5:10">
       <c r="F104" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>273</v>
       </c>
       <c r="I104" s="7">
-        <v>1.33</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887B6AC6-CE14-4411-B244-BD698AC8412D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3135F5-49E9-4A94-8864-5F757430CA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -838,9 +838,6 @@
     <t>elc_spv_rapla</t>
   </si>
   <si>
-    <t>elv_spv_laane</t>
-  </si>
-  <si>
     <t>solar electricity generation in Voru</t>
   </si>
   <si>
@@ -856,10 +853,13 @@
     <t>solar electricity generation in hiiu</t>
   </si>
   <si>
-    <t>elv_spv_hiiu</t>
-  </si>
-  <si>
     <t>EUR25</t>
+  </si>
+  <si>
+    <t>elc_spv_laane</t>
+  </si>
+  <si>
+    <t>elc_spv_hiiu</t>
   </si>
 </sst>
 </file>
@@ -3219,15 +3219,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3294,23 +3294,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:W37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.7265625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" ht="18" thickBot="1">
+    <row r="3" spans="2:23" ht="17.5" thickBot="1">
       <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="2:23" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:23" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>263</v>
       </c>
       <c r="O15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3793,7 +3793,7 @@
         <v>264</v>
       </c>
       <c r="O16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3825,7 +3825,7 @@
         <v>265</v>
       </c>
       <c r="O17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -3854,10 +3854,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -3886,10 +3886,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4210,15 +4210,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="14.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="9.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="2"/>
+    <col min="4" max="4" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -4249,7 +4249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15">
+    <row r="12" spans="2:7" ht="14.5">
       <c r="B12" s="3" t="s">
         <v>215</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15">
+    <row r="13" spans="2:7" ht="14.5">
       <c r="B13" s="5">
         <v>1</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15">
+    <row r="14" spans="2:7" ht="14.5">
       <c r="B14" s="5">
         <v>5</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15">
+    <row r="15" spans="2:7" ht="14.5">
       <c r="B15" s="5">
         <v>5</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15">
+    <row r="16" spans="2:7" ht="14.5">
       <c r="B16" s="5">
         <v>5</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15">
+    <row r="17" spans="2:7" ht="14.5">
       <c r="B17" s="5">
         <v>5</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15">
+    <row r="18" spans="2:7" ht="14.5">
       <c r="B18" s="5">
         <v>5</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15">
+    <row r="19" spans="2:7" ht="14.5">
       <c r="B19" s="5">
         <v>5</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15">
+    <row r="20" spans="2:7" ht="14.5">
       <c r="B20" s="5"/>
       <c r="D20" s="2" t="s">
         <v>46</v>
@@ -4397,70 +4397,70 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15">
+    <row r="21" spans="2:7" ht="14.5">
       <c r="B21" s="5"/>
       <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15">
+    <row r="22" spans="2:7" ht="14.5">
       <c r="B22" s="5"/>
       <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15">
+    <row r="23" spans="2:7" ht="14.5">
       <c r="B23" s="5"/>
       <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15">
+    <row r="24" spans="2:7" ht="14.5">
       <c r="B24" s="5"/>
       <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15">
+    <row r="25" spans="2:7" ht="14.5">
       <c r="B25" s="5"/>
       <c r="D25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15">
+    <row r="26" spans="2:7" ht="14.5">
       <c r="B26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15">
+    <row r="27" spans="2:7" ht="14.5">
       <c r="B27" s="5"/>
       <c r="D27" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15">
+    <row r="28" spans="2:7" ht="14.5">
       <c r="B28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="15">
+    <row r="29" spans="2:7" ht="14.5">
       <c r="B29" s="5"/>
       <c r="D29" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="15">
+    <row r="30" spans="2:7" ht="14.5">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="2:7" ht="15">
+    <row r="31" spans="2:7" ht="14.5">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="2:7" ht="15">
+    <row r="32" spans="2:7" ht="14.5">
       <c r="B32" s="5"/>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" spans="2:2" ht="14.5">
       <c r="B33" s="5"/>
     </row>
   </sheetData>
@@ -4472,28 +4472,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
-    <col min="2" max="2" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7"/>
+    <col min="2" max="2" width="8.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="7"/>
+    <col min="9" max="9" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.453125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
+    <row r="1" spans="2:12" ht="12.5">
       <c r="B1" s="2"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="2:12" ht="12.75">
+    <row r="2" spans="2:12" ht="12.5">
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4504,7 +4504,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="2:12" ht="12.75">
+    <row r="3" spans="2:12" ht="12.5">
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
@@ -4523,7 +4523,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" ht="12">
       <c r="B5" s="11" t="s">
         <v>48</v>
       </c>
@@ -4632,7 +4632,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" ht="12">
       <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.75">
+    <row r="18" spans="2:14" ht="12.5">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -4691,7 +4691,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="2:14" ht="12.75">
+    <row r="19" spans="2:14" ht="12.5">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -4702,7 +4702,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="2:14" ht="12.75">
+    <row r="20" spans="2:14" ht="12.5">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -4713,7 +4713,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
+    <row r="21" spans="2:14" ht="14.5">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -4728,7 +4728,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="15">
+    <row r="22" spans="2:14" ht="14.5">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -4743,7 +4743,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="15">
+    <row r="23" spans="2:14" ht="14.5">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -4758,7 +4758,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="15">
+    <row r="24" spans="2:14" ht="14.5">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -4773,7 +4773,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="15">
+    <row r="25" spans="2:14" ht="14.5">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4788,7 +4788,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="15">
+    <row r="26" spans="2:14" ht="14.5">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4803,7 +4803,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="15">
+    <row r="27" spans="2:14" ht="14.5">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4818,7 +4818,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="15">
+    <row r="28" spans="2:14" ht="14.5">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4833,7 +4833,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="15">
+    <row r="29" spans="2:14" ht="14.5">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4848,7 +4848,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="15">
+    <row r="30" spans="2:14" ht="14.5">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4863,7 +4863,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="15">
+    <row r="31" spans="2:14" ht="14.5">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -4878,7 +4878,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="15">
+    <row r="32" spans="2:14" ht="14.5">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -4893,7 +4893,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="15">
+    <row r="33" spans="2:14" ht="14.5">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -4908,7 +4908,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="15">
+    <row r="34" spans="2:14" ht="14.5">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -4923,7 +4923,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="15">
+    <row r="35" spans="2:14" ht="14.5">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -4938,7 +4938,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="15">
+    <row r="36" spans="2:14" ht="14.5">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -4953,7 +4953,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="15">
+    <row r="37" spans="2:14" ht="14.5">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -4968,7 +4968,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="15">
+    <row r="38" spans="2:14" ht="14.5">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -4983,7 +4983,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="15">
+    <row r="39" spans="2:14" ht="14.5">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -4998,7 +4998,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="15">
+    <row r="40" spans="2:14" ht="14.5">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -5013,7 +5013,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="15">
+    <row r="41" spans="2:14" ht="14.5">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -5028,7 +5028,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="15">
+    <row r="42" spans="2:14" ht="14.5">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -5053,25 +5053,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N104"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
-    <col min="2" max="2" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="7"/>
-    <col min="5" max="5" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7"/>
+    <col min="2" max="2" width="12.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" style="7"/>
+    <col min="5" max="5" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="7"/>
-    <col min="12" max="12" width="17.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="7"/>
+    <col min="10" max="10" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" style="7"/>
+    <col min="12" max="12" width="17.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.453125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="18" thickBot="1">
+    <row r="2" spans="1:14" ht="17.5" thickBot="1">
       <c r="A2" s="9"/>
       <c r="B2" s="16" t="s">
         <v>68</v>
@@ -5085,7 +5085,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="15.5" thickTop="1" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="1" t="s">
         <v>70</v>
@@ -5118,7 +5118,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13">
       <c r="A4" s="9"/>
       <c r="B4" s="15" t="s">
         <v>134</v>
@@ -5143,7 +5143,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13">
       <c r="A5" s="9"/>
       <c r="B5" s="15" t="s">
         <v>72</v>
@@ -5170,7 +5170,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13">
       <c r="A6" s="9"/>
       <c r="B6" s="15" t="s">
         <v>73</v>
@@ -5191,7 +5191,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13">
       <c r="A7" s="9"/>
       <c r="B7" s="15" t="s">
         <v>74</v>
@@ -5212,7 +5212,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13">
       <c r="A8" s="9"/>
       <c r="B8" s="15" t="s">
         <v>75</v>
@@ -5239,7 +5239,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13">
       <c r="A9" s="9"/>
       <c r="B9" s="15" t="s">
         <v>76</v>
@@ -5266,7 +5266,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13">
       <c r="A10" s="9"/>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -5293,7 +5293,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13">
       <c r="A11" s="9"/>
       <c r="B11" s="15" t="s">
         <v>71</v>
@@ -5320,7 +5320,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13">
       <c r="A12" s="9"/>
       <c r="B12" s="15" t="s">
         <v>82</v>
@@ -5347,7 +5347,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13">
       <c r="A13" s="9"/>
       <c r="B13" s="15" t="s">
         <v>85</v>
@@ -5374,7 +5374,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13">
       <c r="A14" s="9"/>
       <c r="B14" s="15" t="s">
         <v>87</v>
@@ -5401,7 +5401,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13">
       <c r="A15" s="9"/>
       <c r="B15" s="15" t="s">
         <v>90</v>
@@ -5428,7 +5428,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13">
       <c r="A16" s="9"/>
       <c r="B16" s="15" t="s">
         <v>93</v>
@@ -5455,7 +5455,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13">
       <c r="A17" s="9"/>
       <c r="B17" s="15" t="s">
         <v>95</v>
@@ -5482,7 +5482,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13">
       <c r="B18" s="15" t="s">
         <v>97</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13">
       <c r="B19" s="15" t="s">
         <v>99</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13">
       <c r="B20" s="15" t="s">
         <v>101</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13">
       <c r="B21" s="15" t="s">
         <v>103</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13">
       <c r="B22" s="15" t="s">
         <v>106</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13">
       <c r="B23" s="15" t="s">
         <v>109</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13">
       <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13">
       <c r="B25" s="15" t="s">
         <v>114</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13">
       <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13">
       <c r="B27" s="15" t="s">
         <v>118</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13">
       <c r="B28" s="15" t="s">
         <v>121</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.5">
+    <row r="29" spans="1:14" ht="13">
       <c r="B29" s="15" t="s">
         <v>123</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.5">
+    <row r="30" spans="1:14" ht="13">
       <c r="B30" s="15" t="s">
         <v>124</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.5">
+    <row r="31" spans="1:14" ht="13">
       <c r="B31" s="15" t="s">
         <v>126</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.5">
+    <row r="32" spans="1:14" ht="13">
       <c r="B32" s="15" t="s">
         <v>128</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.5">
+    <row r="33" spans="2:9" ht="13">
       <c r="B33" s="15" t="s">
         <v>130</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5">
+    <row r="34" spans="2:9" ht="13">
       <c r="B34" s="15" t="s">
         <v>132</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5">
+    <row r="35" spans="2:9" ht="13">
       <c r="B35" s="15" t="s">
         <v>133</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.5">
+    <row r="36" spans="2:9" ht="13">
       <c r="B36" s="15" t="s">
         <v>134</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.5">
+    <row r="37" spans="2:9" ht="13">
       <c r="B37" s="15" t="s">
         <v>135</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.5">
+    <row r="38" spans="2:9" ht="13">
       <c r="B38" s="15" t="s">
         <v>136</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5">
+    <row r="39" spans="2:9" ht="13">
       <c r="B39" s="15" t="s">
         <v>137</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.5">
+    <row r="40" spans="2:9" ht="13">
       <c r="B40" s="15" t="s">
         <v>138</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.5">
+    <row r="41" spans="2:9" ht="13">
       <c r="B41" s="15" t="s">
         <v>139</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.5">
+    <row r="42" spans="2:9" ht="13">
       <c r="B42" s="15" t="s">
         <v>140</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.5">
+    <row r="43" spans="2:9" ht="13">
       <c r="B43" s="15" t="s">
         <v>141</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.5">
+    <row r="44" spans="2:9" ht="13">
       <c r="B44" s="15" t="s">
         <v>142</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.5">
+    <row r="45" spans="2:9" ht="13">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.5">
+    <row r="46" spans="2:9" ht="13">
       <c r="B46" s="15" t="s">
         <v>144</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.5">
+    <row r="47" spans="2:9" ht="13">
       <c r="B47" s="15" t="s">
         <v>145</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.5">
+    <row r="48" spans="2:9" ht="13">
       <c r="B48" s="15" t="s">
         <v>146</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.5">
+    <row r="49" spans="2:9" ht="13">
       <c r="B49" s="15" t="s">
         <v>147</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.5">
+    <row r="50" spans="2:9" ht="13">
       <c r="B50" s="15" t="s">
         <v>148</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.5">
+    <row r="51" spans="2:9" ht="13">
       <c r="B51" s="15" t="s">
         <v>149</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.5">
+    <row r="52" spans="2:9" ht="13">
       <c r="B52" s="15" t="s">
         <v>150</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.5">
+    <row r="53" spans="2:9" ht="13">
       <c r="B53" s="15" t="s">
         <v>151</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.5">
+    <row r="54" spans="2:9" ht="13">
       <c r="B54" s="15" t="s">
         <v>152</v>
       </c>
@@ -6179,7 +6179,7 @@
     </row>
     <row r="55" spans="2:9">
       <c r="B55" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>191</v>
@@ -6632,12 +6632,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="18" thickBot="1">
+    <row r="99" spans="5:10" ht="17.5" thickBot="1">
       <c r="E99" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="15.5" thickTop="1" thickBot="1">
       <c r="E100" s="1" t="s">
         <v>48</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="15">
+    <row r="101" spans="5:10" ht="14.5">
       <c r="E101"/>
       <c r="F101" s="17" t="s">
         <v>189</v>
@@ -6673,7 +6673,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="15">
+    <row r="102" spans="5:10" ht="14.5">
       <c r="E102"/>
       <c r="F102" s="17" t="s">
         <v>191</v>
@@ -6695,7 +6695,7 @@
         <v>73</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I103" s="7">
         <v>1.33</v>
@@ -6706,7 +6706,7 @@
         <v>191</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I104" s="7">
         <v>7.0000000000000007E-2</v>
@@ -6721,19 +6721,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="2"/>
-    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="2" width="8.81640625" style="2"/>
+    <col min="3" max="3" width="20.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18" thickBot="1">
+    <row r="3" spans="2:4" ht="17.5" thickBot="1">
       <c r="B3" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B4" s="1" t="s">
         <v>50</v>
       </c>
@@ -6920,17 +6920,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" ht="13">
       <c r="B23" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="18" thickBot="1">
+    <row r="25" spans="2:4" ht="17.5" thickBot="1">
       <c r="B25" s="16" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="15.5" thickTop="1" thickBot="1">
       <c r="B26" s="1" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_EST/SysSettings.xlsx
+++ b/VerveStacks_EST/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3135F5-49E9-4A94-8864-5F757430CA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9863DA41-8A5E-42BE-B190-F410B134209D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="275">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -860,6 +860,9 @@
   </si>
   <si>
     <t>elc_spv_hiiu</t>
+  </si>
+  <si>
+    <t>flo_fr</t>
   </si>
 </sst>
 </file>
@@ -4624,6 +4627,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12" spans="2:12">
+      <c r="D12" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>5</v>
+      </c>
+    </row>
     <row r="14" spans="2:12">
       <c r="B14" s="10" t="s">
         <v>62</v>
